--- a/products-storage/04-polnyy-komplekt-pto/01-30-bazovye-pakety/01-zakrytie-rabot/14-raschet-procentov-395-gk.xlsx
+++ b/products-storage/04-polnyy-komplekt-pto/01-30-bazovye-pakety/01-zakrytie-rabot/14-raschet-procentov-395-gk.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="DD.MM.YYYY"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,6 +57,12 @@
     </font>
     <font>
       <name val="Times New Roman"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
       <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
@@ -116,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -139,12 +145,13 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -764,7 +771,7 @@
     <row r="47" ht="64" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Частичная оплата по ст. 319 ГК РФ гасит сначала издержки, затем проценты и только потом основной долг. Отступить от этой очерёдности можно соглашением сторон; одностороннее указание в платёжном поручении соглашением не является и очерёдность не меняет. Порядок такой: есть допустимое соглашение — считайте по нему; соглашения нет — по ст. 319 ГК РФ. Если однородных обязательств несколько, выбор погашаемого — отдельный вопрос, и его решают не здесь. Эта таблица уменьшает базу долга на сумму оплаты с её даты, то есть считает по простому варианту: если очерёдность имеет значение для вашего спора, расчёт надо корректировать с юристом.</t>
+          <t>Частичная оплата по ст. 319 ГК РФ гасит сначала издержки, затем проценты и только потом основной долг. Отступить от этой очерёдности можно соглашением сторон; одностороннее указание в платёжном поручении соглашением не является и очерёдность не меняет. Порядок такой: есть допустимое соглашение — считайте по нему; соглашения нет — по ст. 319 ГК РФ. Если однородных обязательств несколько, выбор погашаемого — отдельный вопрос, и его решают не здесь. Эта таблица уменьшает базу долга со дня, следующего за датой оплаты: день оплаты остаётся днём просрочки на прежнюю сумму. Это простой вариант; если очерёдность имеет значение для вашего спора, расчёт надо корректировать с юристом.</t>
         </is>
       </c>
     </row>
@@ -861,7 +868,7 @@
         <v/>
       </c>
       <c r="D4" s="11">
-        <f>IF($A4="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A4,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A4="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A4,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E4" s="12">
@@ -877,7 +884,7 @@
         <v/>
       </c>
       <c r="H4" s="13">
-        <f>IF($A4="","",IF(YEAR($A4)&lt;&gt;YEAR($B4),"Период пересекает 31 декабря — разбейте на две строки",IF($B4&lt;$A4,"Конец периода раньше начала",IF($E4="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A4="","",IF(YEAR($A4)&lt;&gt;YEAR($B4),"Период пересекает 31 декабря — разбейте на две строки",IF($B4&lt;$A4,"Конец периода раньше начала",IF($A4&lt;&gt;'Входные данные'!$B$5,"Период пропущен или перекрыт — исправьте даты",IF($E4="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -889,7 +896,7 @@
         <v/>
       </c>
       <c r="D5" s="11">
-        <f>IF($A5="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A5,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A5="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A5,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E5" s="12">
@@ -905,7 +912,7 @@
         <v/>
       </c>
       <c r="H5" s="13">
-        <f>IF($A5="","",IF(YEAR($A5)&lt;&gt;YEAR($B5),"Период пересекает 31 декабря — разбейте на две строки",IF($B5&lt;$A5,"Конец периода раньше начала",IF($E5="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A5="","",IF(YEAR($A5)&lt;&gt;YEAR($B5),"Период пересекает 31 декабря — разбейте на две строки",IF($B5&lt;$A5,"Конец периода раньше начала",IF(OR($B4="",$A5&lt;&gt;$B4+1),"Период пропущен или перекрыт — исправьте даты",IF($E5="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -917,7 +924,7 @@
         <v/>
       </c>
       <c r="D6" s="11">
-        <f>IF($A6="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A6,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A6="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A6,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E6" s="12">
@@ -933,7 +940,7 @@
         <v/>
       </c>
       <c r="H6" s="13">
-        <f>IF($A6="","",IF(YEAR($A6)&lt;&gt;YEAR($B6),"Период пересекает 31 декабря — разбейте на две строки",IF($B6&lt;$A6,"Конец периода раньше начала",IF($E6="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A6="","",IF(YEAR($A6)&lt;&gt;YEAR($B6),"Период пересекает 31 декабря — разбейте на две строки",IF($B6&lt;$A6,"Конец периода раньше начала",IF(OR($B5="",$A6&lt;&gt;$B5+1),"Период пропущен или перекрыт — исправьте даты",IF($E6="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -945,7 +952,7 @@
         <v/>
       </c>
       <c r="D7" s="11">
-        <f>IF($A7="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A7,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A7="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A7,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E7" s="12">
@@ -961,7 +968,7 @@
         <v/>
       </c>
       <c r="H7" s="13">
-        <f>IF($A7="","",IF(YEAR($A7)&lt;&gt;YEAR($B7),"Период пересекает 31 декабря — разбейте на две строки",IF($B7&lt;$A7,"Конец периода раньше начала",IF($E7="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A7="","",IF(YEAR($A7)&lt;&gt;YEAR($B7),"Период пересекает 31 декабря — разбейте на две строки",IF($B7&lt;$A7,"Конец периода раньше начала",IF(OR($B6="",$A7&lt;&gt;$B6+1),"Период пропущен или перекрыт — исправьте даты",IF($E7="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -973,7 +980,7 @@
         <v/>
       </c>
       <c r="D8" s="11">
-        <f>IF($A8="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A8,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A8="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A8,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E8" s="12">
@@ -989,7 +996,7 @@
         <v/>
       </c>
       <c r="H8" s="13">
-        <f>IF($A8="","",IF(YEAR($A8)&lt;&gt;YEAR($B8),"Период пересекает 31 декабря — разбейте на две строки",IF($B8&lt;$A8,"Конец периода раньше начала",IF($E8="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A8="","",IF(YEAR($A8)&lt;&gt;YEAR($B8),"Период пересекает 31 декабря — разбейте на две строки",IF($B8&lt;$A8,"Конец периода раньше начала",IF(OR($B7="",$A8&lt;&gt;$B7+1),"Период пропущен или перекрыт — исправьте даты",IF($E8="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1001,7 +1008,7 @@
         <v/>
       </c>
       <c r="D9" s="11">
-        <f>IF($A9="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A9,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A9="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A9,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E9" s="12">
@@ -1017,7 +1024,7 @@
         <v/>
       </c>
       <c r="H9" s="13">
-        <f>IF($A9="","",IF(YEAR($A9)&lt;&gt;YEAR($B9),"Период пересекает 31 декабря — разбейте на две строки",IF($B9&lt;$A9,"Конец периода раньше начала",IF($E9="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A9="","",IF(YEAR($A9)&lt;&gt;YEAR($B9),"Период пересекает 31 декабря — разбейте на две строки",IF($B9&lt;$A9,"Конец периода раньше начала",IF(OR($B8="",$A9&lt;&gt;$B8+1),"Период пропущен или перекрыт — исправьте даты",IF($E9="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1029,7 +1036,7 @@
         <v/>
       </c>
       <c r="D10" s="11">
-        <f>IF($A10="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A10,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A10="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A10,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E10" s="12">
@@ -1045,7 +1052,7 @@
         <v/>
       </c>
       <c r="H10" s="13">
-        <f>IF($A10="","",IF(YEAR($A10)&lt;&gt;YEAR($B10),"Период пересекает 31 декабря — разбейте на две строки",IF($B10&lt;$A10,"Конец периода раньше начала",IF($E10="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A10="","",IF(YEAR($A10)&lt;&gt;YEAR($B10),"Период пересекает 31 декабря — разбейте на две строки",IF($B10&lt;$A10,"Конец периода раньше начала",IF(OR($B9="",$A10&lt;&gt;$B9+1),"Период пропущен или перекрыт — исправьте даты",IF($E10="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1057,7 +1064,7 @@
         <v/>
       </c>
       <c r="D11" s="11">
-        <f>IF($A11="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A11,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A11="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A11,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E11" s="12">
@@ -1073,7 +1080,7 @@
         <v/>
       </c>
       <c r="H11" s="13">
-        <f>IF($A11="","",IF(YEAR($A11)&lt;&gt;YEAR($B11),"Период пересекает 31 декабря — разбейте на две строки",IF($B11&lt;$A11,"Конец периода раньше начала",IF($E11="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A11="","",IF(YEAR($A11)&lt;&gt;YEAR($B11),"Период пересекает 31 декабря — разбейте на две строки",IF($B11&lt;$A11,"Конец периода раньше начала",IF(OR($B10="",$A11&lt;&gt;$B10+1),"Период пропущен или перекрыт — исправьте даты",IF($E11="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1085,7 +1092,7 @@
         <v/>
       </c>
       <c r="D12" s="11">
-        <f>IF($A12="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A12,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A12="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A12,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E12" s="12">
@@ -1101,7 +1108,7 @@
         <v/>
       </c>
       <c r="H12" s="13">
-        <f>IF($A12="","",IF(YEAR($A12)&lt;&gt;YEAR($B12),"Период пересекает 31 декабря — разбейте на две строки",IF($B12&lt;$A12,"Конец периода раньше начала",IF($E12="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A12="","",IF(YEAR($A12)&lt;&gt;YEAR($B12),"Период пересекает 31 декабря — разбейте на две строки",IF($B12&lt;$A12,"Конец периода раньше начала",IF(OR($B11="",$A12&lt;&gt;$B11+1),"Период пропущен или перекрыт — исправьте даты",IF($E12="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1113,7 +1120,7 @@
         <v/>
       </c>
       <c r="D13" s="11">
-        <f>IF($A13="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A13,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A13="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A13,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E13" s="12">
@@ -1129,7 +1136,7 @@
         <v/>
       </c>
       <c r="H13" s="13">
-        <f>IF($A13="","",IF(YEAR($A13)&lt;&gt;YEAR($B13),"Период пересекает 31 декабря — разбейте на две строки",IF($B13&lt;$A13,"Конец периода раньше начала",IF($E13="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A13="","",IF(YEAR($A13)&lt;&gt;YEAR($B13),"Период пересекает 31 декабря — разбейте на две строки",IF($B13&lt;$A13,"Конец периода раньше начала",IF(OR($B12="",$A13&lt;&gt;$B12+1),"Период пропущен или перекрыт — исправьте даты",IF($E13="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1141,7 +1148,7 @@
         <v/>
       </c>
       <c r="D14" s="11">
-        <f>IF($A14="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A14,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A14="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A14,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E14" s="12">
@@ -1157,7 +1164,7 @@
         <v/>
       </c>
       <c r="H14" s="13">
-        <f>IF($A14="","",IF(YEAR($A14)&lt;&gt;YEAR($B14),"Период пересекает 31 декабря — разбейте на две строки",IF($B14&lt;$A14,"Конец периода раньше начала",IF($E14="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A14="","",IF(YEAR($A14)&lt;&gt;YEAR($B14),"Период пересекает 31 декабря — разбейте на две строки",IF($B14&lt;$A14,"Конец периода раньше начала",IF(OR($B13="",$A14&lt;&gt;$B13+1),"Период пропущен или перекрыт — исправьте даты",IF($E14="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1169,7 +1176,7 @@
         <v/>
       </c>
       <c r="D15" s="11">
-        <f>IF($A15="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A15,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A15="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A15,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E15" s="12">
@@ -1185,7 +1192,7 @@
         <v/>
       </c>
       <c r="H15" s="13">
-        <f>IF($A15="","",IF(YEAR($A15)&lt;&gt;YEAR($B15),"Период пересекает 31 декабря — разбейте на две строки",IF($B15&lt;$A15,"Конец периода раньше начала",IF($E15="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A15="","",IF(YEAR($A15)&lt;&gt;YEAR($B15),"Период пересекает 31 декабря — разбейте на две строки",IF($B15&lt;$A15,"Конец периода раньше начала",IF(OR($B14="",$A15&lt;&gt;$B14+1),"Период пропущен или перекрыт — исправьте даты",IF($E15="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1197,7 +1204,7 @@
         <v/>
       </c>
       <c r="D16" s="11">
-        <f>IF($A16="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A16,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A16="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A16,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E16" s="12">
@@ -1213,7 +1220,7 @@
         <v/>
       </c>
       <c r="H16" s="13">
-        <f>IF($A16="","",IF(YEAR($A16)&lt;&gt;YEAR($B16),"Период пересекает 31 декабря — разбейте на две строки",IF($B16&lt;$A16,"Конец периода раньше начала",IF($E16="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A16="","",IF(YEAR($A16)&lt;&gt;YEAR($B16),"Период пересекает 31 декабря — разбейте на две строки",IF($B16&lt;$A16,"Конец периода раньше начала",IF(OR($B15="",$A16&lt;&gt;$B15+1),"Период пропущен или перекрыт — исправьте даты",IF($E16="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1225,7 +1232,7 @@
         <v/>
       </c>
       <c r="D17" s="11">
-        <f>IF($A17="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A17,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A17="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A17,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E17" s="12">
@@ -1241,7 +1248,7 @@
         <v/>
       </c>
       <c r="H17" s="13">
-        <f>IF($A17="","",IF(YEAR($A17)&lt;&gt;YEAR($B17),"Период пересекает 31 декабря — разбейте на две строки",IF($B17&lt;$A17,"Конец периода раньше начала",IF($E17="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A17="","",IF(YEAR($A17)&lt;&gt;YEAR($B17),"Период пересекает 31 декабря — разбейте на две строки",IF($B17&lt;$A17,"Конец периода раньше начала",IF(OR($B16="",$A17&lt;&gt;$B16+1),"Период пропущен или перекрыт — исправьте даты",IF($E17="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1253,7 +1260,7 @@
         <v/>
       </c>
       <c r="D18" s="11">
-        <f>IF($A18="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A18,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A18="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A18,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E18" s="12">
@@ -1269,7 +1276,7 @@
         <v/>
       </c>
       <c r="H18" s="13">
-        <f>IF($A18="","",IF(YEAR($A18)&lt;&gt;YEAR($B18),"Период пересекает 31 декабря — разбейте на две строки",IF($B18&lt;$A18,"Конец периода раньше начала",IF($E18="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A18="","",IF(YEAR($A18)&lt;&gt;YEAR($B18),"Период пересекает 31 декабря — разбейте на две строки",IF($B18&lt;$A18,"Конец периода раньше начала",IF(OR($B17="",$A18&lt;&gt;$B17+1),"Период пропущен или перекрыт — исправьте даты",IF($E18="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1281,7 +1288,7 @@
         <v/>
       </c>
       <c r="D19" s="11">
-        <f>IF($A19="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A19,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A19="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A19,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E19" s="12">
@@ -1297,7 +1304,7 @@
         <v/>
       </c>
       <c r="H19" s="13">
-        <f>IF($A19="","",IF(YEAR($A19)&lt;&gt;YEAR($B19),"Период пересекает 31 декабря — разбейте на две строки",IF($B19&lt;$A19,"Конец периода раньше начала",IF($E19="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A19="","",IF(YEAR($A19)&lt;&gt;YEAR($B19),"Период пересекает 31 декабря — разбейте на две строки",IF($B19&lt;$A19,"Конец периода раньше начала",IF(OR($B18="",$A19&lt;&gt;$B18+1),"Период пропущен или перекрыт — исправьте даты",IF($E19="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1309,7 +1316,7 @@
         <v/>
       </c>
       <c r="D20" s="11">
-        <f>IF($A20="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A20,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A20="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A20,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E20" s="12">
@@ -1325,7 +1332,7 @@
         <v/>
       </c>
       <c r="H20" s="13">
-        <f>IF($A20="","",IF(YEAR($A20)&lt;&gt;YEAR($B20),"Период пересекает 31 декабря — разбейте на две строки",IF($B20&lt;$A20,"Конец периода раньше начала",IF($E20="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A20="","",IF(YEAR($A20)&lt;&gt;YEAR($B20),"Период пересекает 31 декабря — разбейте на две строки",IF($B20&lt;$A20,"Конец периода раньше начала",IF(OR($B19="",$A20&lt;&gt;$B19+1),"Период пропущен или перекрыт — исправьте даты",IF($E20="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1337,7 +1344,7 @@
         <v/>
       </c>
       <c r="D21" s="11">
-        <f>IF($A21="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A21,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A21="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A21,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E21" s="12">
@@ -1353,7 +1360,7 @@
         <v/>
       </c>
       <c r="H21" s="13">
-        <f>IF($A21="","",IF(YEAR($A21)&lt;&gt;YEAR($B21),"Период пересекает 31 декабря — разбейте на две строки",IF($B21&lt;$A21,"Конец периода раньше начала",IF($E21="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A21="","",IF(YEAR($A21)&lt;&gt;YEAR($B21),"Период пересекает 31 декабря — разбейте на две строки",IF($B21&lt;$A21,"Конец периода раньше начала",IF(OR($B20="",$A21&lt;&gt;$B20+1),"Период пропущен или перекрыт — исправьте даты",IF($E21="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1365,7 +1372,7 @@
         <v/>
       </c>
       <c r="D22" s="11">
-        <f>IF($A22="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A22,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A22="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A22,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E22" s="12">
@@ -1381,7 +1388,7 @@
         <v/>
       </c>
       <c r="H22" s="13">
-        <f>IF($A22="","",IF(YEAR($A22)&lt;&gt;YEAR($B22),"Период пересекает 31 декабря — разбейте на две строки",IF($B22&lt;$A22,"Конец периода раньше начала",IF($E22="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A22="","",IF(YEAR($A22)&lt;&gt;YEAR($B22),"Период пересекает 31 декабря — разбейте на две строки",IF($B22&lt;$A22,"Конец периода раньше начала",IF(OR($B21="",$A22&lt;&gt;$B21+1),"Период пропущен или перекрыт — исправьте даты",IF($E22="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1393,7 +1400,7 @@
         <v/>
       </c>
       <c r="D23" s="11">
-        <f>IF($A23="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A23,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A23="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A23,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E23" s="12">
@@ -1409,7 +1416,7 @@
         <v/>
       </c>
       <c r="H23" s="13">
-        <f>IF($A23="","",IF(YEAR($A23)&lt;&gt;YEAR($B23),"Период пересекает 31 декабря — разбейте на две строки",IF($B23&lt;$A23,"Конец периода раньше начала",IF($E23="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A23="","",IF(YEAR($A23)&lt;&gt;YEAR($B23),"Период пересекает 31 декабря — разбейте на две строки",IF($B23&lt;$A23,"Конец периода раньше начала",IF(OR($B22="",$A23&lt;&gt;$B22+1),"Период пропущен или перекрыт — исправьте даты",IF($E23="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1421,7 +1428,7 @@
         <v/>
       </c>
       <c r="D24" s="11">
-        <f>IF($A24="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A24,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A24="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A24,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E24" s="12">
@@ -1437,7 +1444,7 @@
         <v/>
       </c>
       <c r="H24" s="13">
-        <f>IF($A24="","",IF(YEAR($A24)&lt;&gt;YEAR($B24),"Период пересекает 31 декабря — разбейте на две строки",IF($B24&lt;$A24,"Конец периода раньше начала",IF($E24="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A24="","",IF(YEAR($A24)&lt;&gt;YEAR($B24),"Период пересекает 31 декабря — разбейте на две строки",IF($B24&lt;$A24,"Конец периода раньше начала",IF(OR($B23="",$A24&lt;&gt;$B23+1),"Период пропущен или перекрыт — исправьте даты",IF($E24="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1449,7 +1456,7 @@
         <v/>
       </c>
       <c r="D25" s="11">
-        <f>IF($A25="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A25,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A25="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A25,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E25" s="12">
@@ -1465,7 +1472,7 @@
         <v/>
       </c>
       <c r="H25" s="13">
-        <f>IF($A25="","",IF(YEAR($A25)&lt;&gt;YEAR($B25),"Период пересекает 31 декабря — разбейте на две строки",IF($B25&lt;$A25,"Конец периода раньше начала",IF($E25="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A25="","",IF(YEAR($A25)&lt;&gt;YEAR($B25),"Период пересекает 31 декабря — разбейте на две строки",IF($B25&lt;$A25,"Конец периода раньше начала",IF(OR($B24="",$A25&lt;&gt;$B24+1),"Период пропущен или перекрыт — исправьте даты",IF($E25="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1477,7 +1484,7 @@
         <v/>
       </c>
       <c r="D26" s="11">
-        <f>IF($A26="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A26,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A26="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A26,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E26" s="12">
@@ -1493,7 +1500,7 @@
         <v/>
       </c>
       <c r="H26" s="13">
-        <f>IF($A26="","",IF(YEAR($A26)&lt;&gt;YEAR($B26),"Период пересекает 31 декабря — разбейте на две строки",IF($B26&lt;$A26,"Конец периода раньше начала",IF($E26="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A26="","",IF(YEAR($A26)&lt;&gt;YEAR($B26),"Период пересекает 31 декабря — разбейте на две строки",IF($B26&lt;$A26,"Конец периода раньше начала",IF(OR($B25="",$A26&lt;&gt;$B25+1),"Период пропущен или перекрыт — исправьте даты",IF($E26="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1505,7 +1512,7 @@
         <v/>
       </c>
       <c r="D27" s="11">
-        <f>IF($A27="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A27,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A27="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A27,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E27" s="12">
@@ -1521,7 +1528,7 @@
         <v/>
       </c>
       <c r="H27" s="13">
-        <f>IF($A27="","",IF(YEAR($A27)&lt;&gt;YEAR($B27),"Период пересекает 31 декабря — разбейте на две строки",IF($B27&lt;$A27,"Конец периода раньше начала",IF($E27="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A27="","",IF(YEAR($A27)&lt;&gt;YEAR($B27),"Период пересекает 31 декабря — разбейте на две строки",IF($B27&lt;$A27,"Конец периода раньше начала",IF(OR($B26="",$A27&lt;&gt;$B26+1),"Период пропущен или перекрыт — исправьте даты",IF($E27="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1533,7 +1540,7 @@
         <v/>
       </c>
       <c r="D28" s="11">
-        <f>IF($A28="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A28,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A28="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A28,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E28" s="12">
@@ -1549,7 +1556,7 @@
         <v/>
       </c>
       <c r="H28" s="13">
-        <f>IF($A28="","",IF(YEAR($A28)&lt;&gt;YEAR($B28),"Период пересекает 31 декабря — разбейте на две строки",IF($B28&lt;$A28,"Конец периода раньше начала",IF($E28="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A28="","",IF(YEAR($A28)&lt;&gt;YEAR($B28),"Период пересекает 31 декабря — разбейте на две строки",IF($B28&lt;$A28,"Конец периода раньше начала",IF(OR($B27="",$A28&lt;&gt;$B27+1),"Период пропущен или перекрыт — исправьте даты",IF($E28="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1561,7 +1568,7 @@
         <v/>
       </c>
       <c r="D29" s="11">
-        <f>IF($A29="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A29,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A29="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A29,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E29" s="12">
@@ -1577,7 +1584,7 @@
         <v/>
       </c>
       <c r="H29" s="13">
-        <f>IF($A29="","",IF(YEAR($A29)&lt;&gt;YEAR($B29),"Период пересекает 31 декабря — разбейте на две строки",IF($B29&lt;$A29,"Конец периода раньше начала",IF($E29="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A29="","",IF(YEAR($A29)&lt;&gt;YEAR($B29),"Период пересекает 31 декабря — разбейте на две строки",IF($B29&lt;$A29,"Конец периода раньше начала",IF(OR($B28="",$A29&lt;&gt;$B28+1),"Период пропущен или перекрыт — исправьте даты",IF($E29="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1589,7 +1596,7 @@
         <v/>
       </c>
       <c r="D30" s="11">
-        <f>IF($A30="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A30,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A30="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A30,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E30" s="12">
@@ -1605,7 +1612,7 @@
         <v/>
       </c>
       <c r="H30" s="13">
-        <f>IF($A30="","",IF(YEAR($A30)&lt;&gt;YEAR($B30),"Период пересекает 31 декабря — разбейте на две строки",IF($B30&lt;$A30,"Конец периода раньше начала",IF($E30="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A30="","",IF(YEAR($A30)&lt;&gt;YEAR($B30),"Период пересекает 31 декабря — разбейте на две строки",IF($B30&lt;$A30,"Конец периода раньше начала",IF(OR($B29="",$A30&lt;&gt;$B29+1),"Период пропущен или перекрыт — исправьте даты",IF($E30="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1617,7 +1624,7 @@
         <v/>
       </c>
       <c r="D31" s="11">
-        <f>IF($A31="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A31,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A31="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A31,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E31" s="12">
@@ -1633,7 +1640,7 @@
         <v/>
       </c>
       <c r="H31" s="13">
-        <f>IF($A31="","",IF(YEAR($A31)&lt;&gt;YEAR($B31),"Период пересекает 31 декабря — разбейте на две строки",IF($B31&lt;$A31,"Конец периода раньше начала",IF($E31="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A31="","",IF(YEAR($A31)&lt;&gt;YEAR($B31),"Период пересекает 31 декабря — разбейте на две строки",IF($B31&lt;$A31,"Конец периода раньше начала",IF(OR($B30="",$A31&lt;&gt;$B30+1),"Период пропущен или перекрыт — исправьте даты",IF($E31="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1645,7 +1652,7 @@
         <v/>
       </c>
       <c r="D32" s="11">
-        <f>IF($A32="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A32,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A32="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A32,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E32" s="12">
@@ -1661,7 +1668,7 @@
         <v/>
       </c>
       <c r="H32" s="13">
-        <f>IF($A32="","",IF(YEAR($A32)&lt;&gt;YEAR($B32),"Период пересекает 31 декабря — разбейте на две строки",IF($B32&lt;$A32,"Конец периода раньше начала",IF($E32="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A32="","",IF(YEAR($A32)&lt;&gt;YEAR($B32),"Период пересекает 31 декабря — разбейте на две строки",IF($B32&lt;$A32,"Конец периода раньше начала",IF(OR($B31="",$A32&lt;&gt;$B31+1),"Период пропущен или перекрыт — исправьте даты",IF($E32="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1673,7 +1680,7 @@
         <v/>
       </c>
       <c r="D33" s="11">
-        <f>IF($A33="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A33,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A33="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A33,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E33" s="12">
@@ -1689,7 +1696,7 @@
         <v/>
       </c>
       <c r="H33" s="13">
-        <f>IF($A33="","",IF(YEAR($A33)&lt;&gt;YEAR($B33),"Период пересекает 31 декабря — разбейте на две строки",IF($B33&lt;$A33,"Конец периода раньше начала",IF($E33="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A33="","",IF(YEAR($A33)&lt;&gt;YEAR($B33),"Период пересекает 31 декабря — разбейте на две строки",IF($B33&lt;$A33,"Конец периода раньше начала",IF(OR($B32="",$A33&lt;&gt;$B32+1),"Период пропущен или перекрыт — исправьте даты",IF($E33="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1701,7 +1708,7 @@
         <v/>
       </c>
       <c r="D34" s="11">
-        <f>IF($A34="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A34,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A34="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A34,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E34" s="12">
@@ -1717,7 +1724,7 @@
         <v/>
       </c>
       <c r="H34" s="13">
-        <f>IF($A34="","",IF(YEAR($A34)&lt;&gt;YEAR($B34),"Период пересекает 31 декабря — разбейте на две строки",IF($B34&lt;$A34,"Конец периода раньше начала",IF($E34="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A34="","",IF(YEAR($A34)&lt;&gt;YEAR($B34),"Период пересекает 31 декабря — разбейте на две строки",IF($B34&lt;$A34,"Конец периода раньше начала",IF(OR($B33="",$A34&lt;&gt;$B33+1),"Период пропущен или перекрыт — исправьте даты",IF($E34="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1729,7 +1736,7 @@
         <v/>
       </c>
       <c r="D35" s="11">
-        <f>IF($A35="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A35,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A35="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A35,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E35" s="12">
@@ -1745,7 +1752,7 @@
         <v/>
       </c>
       <c r="H35" s="13">
-        <f>IF($A35="","",IF(YEAR($A35)&lt;&gt;YEAR($B35),"Период пересекает 31 декабря — разбейте на две строки",IF($B35&lt;$A35,"Конец периода раньше начала",IF($E35="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A35="","",IF(YEAR($A35)&lt;&gt;YEAR($B35),"Период пересекает 31 декабря — разбейте на две строки",IF($B35&lt;$A35,"Конец периода раньше начала",IF(OR($B34="",$A35&lt;&gt;$B34+1),"Период пропущен или перекрыт — исправьте даты",IF($E35="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1757,7 +1764,7 @@
         <v/>
       </c>
       <c r="D36" s="11">
-        <f>IF($A36="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A36,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A36="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A36,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E36" s="12">
@@ -1773,7 +1780,7 @@
         <v/>
       </c>
       <c r="H36" s="13">
-        <f>IF($A36="","",IF(YEAR($A36)&lt;&gt;YEAR($B36),"Период пересекает 31 декабря — разбейте на две строки",IF($B36&lt;$A36,"Конец периода раньше начала",IF($E36="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A36="","",IF(YEAR($A36)&lt;&gt;YEAR($B36),"Период пересекает 31 декабря — разбейте на две строки",IF($B36&lt;$A36,"Конец периода раньше начала",IF(OR($B35="",$A36&lt;&gt;$B35+1),"Период пропущен или перекрыт — исправьте даты",IF($E36="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1785,7 +1792,7 @@
         <v/>
       </c>
       <c r="D37" s="11">
-        <f>IF($A37="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A37,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A37="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A37,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E37" s="12">
@@ -1801,7 +1808,7 @@
         <v/>
       </c>
       <c r="H37" s="13">
-        <f>IF($A37="","",IF(YEAR($A37)&lt;&gt;YEAR($B37),"Период пересекает 31 декабря — разбейте на две строки",IF($B37&lt;$A37,"Конец периода раньше начала",IF($E37="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A37="","",IF(YEAR($A37)&lt;&gt;YEAR($B37),"Период пересекает 31 декабря — разбейте на две строки",IF($B37&lt;$A37,"Конец периода раньше начала",IF(OR($B36="",$A37&lt;&gt;$B36+1),"Период пропущен или перекрыт — исправьте даты",IF($E37="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1813,7 +1820,7 @@
         <v/>
       </c>
       <c r="D38" s="11">
-        <f>IF($A38="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A38,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A38="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A38,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E38" s="12">
@@ -1829,7 +1836,7 @@
         <v/>
       </c>
       <c r="H38" s="13">
-        <f>IF($A38="","",IF(YEAR($A38)&lt;&gt;YEAR($B38),"Период пересекает 31 декабря — разбейте на две строки",IF($B38&lt;$A38,"Конец периода раньше начала",IF($E38="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A38="","",IF(YEAR($A38)&lt;&gt;YEAR($B38),"Период пересекает 31 декабря — разбейте на две строки",IF($B38&lt;$A38,"Конец периода раньше начала",IF(OR($B37="",$A38&lt;&gt;$B37+1),"Период пропущен или перекрыт — исправьте даты",IF($E38="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1841,7 +1848,7 @@
         <v/>
       </c>
       <c r="D39" s="11">
-        <f>IF($A39="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A39,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A39="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A39,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E39" s="12">
@@ -1857,7 +1864,7 @@
         <v/>
       </c>
       <c r="H39" s="13">
-        <f>IF($A39="","",IF(YEAR($A39)&lt;&gt;YEAR($B39),"Период пересекает 31 декабря — разбейте на две строки",IF($B39&lt;$A39,"Конец периода раньше начала",IF($E39="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A39="","",IF(YEAR($A39)&lt;&gt;YEAR($B39),"Период пересекает 31 декабря — разбейте на две строки",IF($B39&lt;$A39,"Конец периода раньше начала",IF(OR($B38="",$A39&lt;&gt;$B38+1),"Период пропущен или перекрыт — исправьте даты",IF($E39="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1869,7 +1876,7 @@
         <v/>
       </c>
       <c r="D40" s="11">
-        <f>IF($A40="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A40,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A40="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A40,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E40" s="12">
@@ -1885,7 +1892,7 @@
         <v/>
       </c>
       <c r="H40" s="13">
-        <f>IF($A40="","",IF(YEAR($A40)&lt;&gt;YEAR($B40),"Период пересекает 31 декабря — разбейте на две строки",IF($B40&lt;$A40,"Конец периода раньше начала",IF($E40="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A40="","",IF(YEAR($A40)&lt;&gt;YEAR($B40),"Период пересекает 31 декабря — разбейте на две строки",IF($B40&lt;$A40,"Конец периода раньше начала",IF(OR($B39="",$A40&lt;&gt;$B39+1),"Период пропущен или перекрыт — исправьте даты",IF($E40="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1897,7 +1904,7 @@
         <v/>
       </c>
       <c r="D41" s="11">
-        <f>IF($A41="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A41,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A41="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A41,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E41" s="12">
@@ -1913,7 +1920,7 @@
         <v/>
       </c>
       <c r="H41" s="13">
-        <f>IF($A41="","",IF(YEAR($A41)&lt;&gt;YEAR($B41),"Период пересекает 31 декабря — разбейте на две строки",IF($B41&lt;$A41,"Конец периода раньше начала",IF($E41="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A41="","",IF(YEAR($A41)&lt;&gt;YEAR($B41),"Период пересекает 31 декабря — разбейте на две строки",IF($B41&lt;$A41,"Конец периода раньше начала",IF(OR($B40="",$A41&lt;&gt;$B40+1),"Период пропущен или перекрыт — исправьте даты",IF($E41="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1925,7 +1932,7 @@
         <v/>
       </c>
       <c r="D42" s="11">
-        <f>IF($A42="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A42,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A42="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A42,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E42" s="12">
@@ -1941,7 +1948,7 @@
         <v/>
       </c>
       <c r="H42" s="13">
-        <f>IF($A42="","",IF(YEAR($A42)&lt;&gt;YEAR($B42),"Период пересекает 31 декабря — разбейте на две строки",IF($B42&lt;$A42,"Конец периода раньше начала",IF($E42="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A42="","",IF(YEAR($A42)&lt;&gt;YEAR($B42),"Период пересекает 31 декабря — разбейте на две строки",IF($B42&lt;$A42,"Конец периода раньше начала",IF(OR($B41="",$A42&lt;&gt;$B41+1),"Период пропущен или перекрыт — исправьте даты",IF($E42="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1953,7 +1960,7 @@
         <v/>
       </c>
       <c r="D43" s="11">
-        <f>IF($A43="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;="&amp;$A43,'Входные данные'!$B$35:$B$44))</f>
+        <f>IF($A43="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A43,'Входные данные'!$B$35:$B$44))</f>
         <v/>
       </c>
       <c r="E43" s="12">
@@ -1969,7 +1976,7 @@
         <v/>
       </c>
       <c r="H43" s="13">
-        <f>IF($A43="","",IF(YEAR($A43)&lt;&gt;YEAR($B43),"Период пересекает 31 декабря — разбейте на две строки",IF($B43&lt;$A43,"Конец периода раньше начала",IF($E43="","Ставка на эту дату не найдена: дополните таблицу ставок",""))))</f>
+        <f>IF($A43="","",IF(YEAR($A43)&lt;&gt;YEAR($B43),"Период пересекает 31 декабря — разбейте на две строки",IF($B43&lt;$A43,"Конец периода раньше начала",IF(OR($B42="",$A43&lt;&gt;$B42+1),"Период пропущен или перекрыт — исправьте даты",IF($E43="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
         <v/>
       </c>
     </row>
@@ -1981,6 +1988,10 @@
       </c>
       <c r="G45" s="15">
         <f>ROUND(SUM($G$4:$G$43),2)</f>
+        <v/>
+      </c>
+      <c r="H45" s="16">
+        <f>IF(COUNT($A$4:$A$43)=0,"",IF(MAX($B$4:$B$43)&lt;&gt;'Входные данные'!$B$6,"Последний период не совпадает с датой окончания",""))</f>
         <v/>
       </c>
     </row>
@@ -2053,89 +2064,89 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Сумма долга на начало расчёта, руб.</t>
         </is>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="18">
         <f>'Входные данные'!$B$4</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Учтено частичных оплат, руб.</t>
         </is>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="18">
         <f>ROUND(SUM('Входные данные'!$B$35:$B$44),2)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Основной долг к взысканию, руб.</t>
         </is>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="18">
         <f>ROUND('Входные данные'!$B$4-SUM('Входные данные'!$B$35:$B$44),2)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Период начисления с</t>
         </is>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="19">
         <f>'Входные данные'!$B$5</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Период начисления по</t>
         </is>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="19">
         <f>'Входные данные'!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Всего дней просрочки</t>
         </is>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="20">
         <f>IF(OR('Входные данные'!$B$5="",'Входные данные'!$B$6=""),"",'Входные данные'!$B$6-'Входные данные'!$B$5+1)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Проценты по ст. 395 ГК РФ, руб.</t>
         </is>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="18">
         <f>'Расчёт'!$G$45</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Итого к взысканию, руб.</t>
         </is>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="18">
         <f>'Расчёт'!$G$46</f>
         <v/>
       </c>
@@ -2148,7 +2159,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>Проценты подлежат начислению по день фактической уплаты долга (п. 3 ст. 395 ГК РФ).</t>
         </is>
@@ -2228,7 +2239,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>Здесь показан формат ввода, а не ваш расчёт. Цифры вымышленные, ставки — условные: реальные берите на cbr.ru. Ничего отсюда не переносите в документ.</t>
         </is>
@@ -2242,36 +2253,36 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Сумма долга, руб.</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>1 250 000,00</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>Дата начала просрочки</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>15.03.2026</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Дата окончания расчёта</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>30.07.2026</t>
         </is>
@@ -2297,24 +2308,24 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>15.03.2026</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>условная 1</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t>28.04.2026</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>условная 2</t>
         </is>
@@ -2370,84 +2381,84 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>15.03.2026</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>27.04.2026</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t>считается</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D16" s="25" t="inlineStr">
         <is>
           <t>считается</t>
         </is>
       </c>
-      <c r="E16" s="24" t="inlineStr">
+      <c r="E16" s="25" t="inlineStr">
         <is>
           <t>подставится</t>
         </is>
       </c>
-      <c r="F16" s="24" t="inlineStr">
+      <c r="F16" s="25" t="inlineStr">
         <is>
           <t>считается</t>
         </is>
       </c>
-      <c r="G16" s="24" t="inlineStr">
+      <c r="G16" s="25" t="inlineStr">
         <is>
           <t>считается</t>
         </is>
       </c>
-      <c r="H16" s="24" t="inlineStr">
+      <c r="H16" s="25" t="inlineStr">
         <is>
           <t>пусто, если всё верно</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>28.04.2026</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>30.07.2026</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t>считается</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="D17" s="25" t="inlineStr">
         <is>
           <t>считается</t>
         </is>
       </c>
-      <c r="E17" s="24" t="inlineStr">
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t>подставится</t>
         </is>
       </c>
-      <c r="F17" s="24" t="inlineStr">
+      <c r="F17" s="25" t="inlineStr">
         <is>
           <t>считается</t>
         </is>
       </c>
-      <c r="G17" s="24" t="inlineStr">
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t>считается</t>
         </is>
       </c>
-      <c r="H17" s="24" t="inlineStr">
+      <c r="H17" s="25" t="inlineStr">
         <is>
           <t>пусто, если всё верно</t>
         </is>

--- a/products-storage/04-polnyy-komplekt-pto/01-30-bazovye-pakety/01-zakrytie-rabot/14-raschet-procentov-395-gk.xlsx
+++ b/products-storage/04-polnyy-komplekt-pto/01-30-bazovye-pakety/01-zakrytie-rabot/14-raschet-procentov-395-gk.xlsx
@@ -1,249 +1,264 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Входные данные" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Расчёт" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Итог для документа" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Пример заполнения" sheetId="4" state="visible" r:id="rId4"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheets>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Входные данные" sheetId="1" r:id="R8705f6fed4154697"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Расчёт" sheetId="2" r:id="R916296fa190a4036"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Итог для документа" sheetId="3" r:id="Rae5eb32b2f5e4c1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Пример заполнения" sheetId="4" r:id="Rd6a7f6e91e0d4e5a"/>
+  </x:sheets>
+</x:workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:authors>
+    <x:author>Маржа в бетоне</x:author>
+  </x:authors>
+  <x:commentList>
+    <x:comment ref="A11" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>Даты вносите по возрастанию: формула ищет ближайшую ставку сверху вниз и на неотсортированном списке даст неверный результат.</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+  </x:commentList>
+</x:comments>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="DD.MM.YYYY"/>
-  </numFmts>
-  <fonts count="10">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <b val="1"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <i val="1"/>
-      <color rgb="00595959"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <color rgb="000000FF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <color rgb="00C00000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <b val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <color rgb="00008000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <i val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="10"/>
-    </font>
-  </fonts>
-  <fills count="4">
-    <fill>
-      <patternFill/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E7E6E6"/>
-      </patternFill>
-    </fill>
-  </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="26">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-  </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
-</styleSheet>
+<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="2">
+    <x:numFmt numFmtId="164" formatCode="DD.MM.YYYY"/>
+    <x:numFmt numFmtId="200" formatCode="DD.MM.YYYY;;"/>
+  </x:numFmts>
+  <x:fonts count="10">
+    <x:font>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:name val="Times New Roman"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF595959"/>
+      <x:name val="Times New Roman"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:name val="Times New Roman"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Times New Roman"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Times New Roman"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FFC00000"/>
+      <x:name val="Times New Roman"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFC00000"/>
+      <x:name val="Times New Roman"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF008000"/>
+      <x:name val="Times New Roman"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FFC00000"/>
+      <x:name val="Times New Roman"/>
+    </x:font>
+  </x:fonts>
+  <x:fills count="4">
+    <x:fill>
+      <x:patternFill patternType="none"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E6E6"/>
+      </x:patternFill>
+    </x:fill>
+  </x:fills>
+  <x:borders count="2">
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFBFBFBF"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFBFBFBF"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFBFBFBF"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFBFBFBF"/>
+      </x:bottom>
+    </x:border>
+  </x:borders>
+  <x:cellStyleXfs count="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </x:cellStyleXfs>
+  <x:cellXfs count="30">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="4" fontId="4" fillId="2" borderId="1" xfId="0"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0"/>
+    <x:xf numFmtId="2" fontId="4" fillId="2" borderId="1" xfId="0"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0"/>
+    <x:xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0"/>
+    <x:xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0"/>
+    <x:xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0"/>
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0"/>
+    <x:xf numFmtId="1" fontId="8" fillId="0" borderId="1" xfId="0"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+  </x:cellXfs>
+  <x:cellStyles count="1">
+    <x:cellStyle name="Normal" xfId="0"/>
+  </x:cellStyles>
+  <x:colors>
+    <x:indexedColors>
+      <x:rgbColor rgb="00000000"/>
+      <x:rgbColor rgb="00FFFFFF"/>
+      <x:rgbColor rgb="00FF0000"/>
+      <x:rgbColor rgb="0000FF00"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00000000"/>
+      <x:rgbColor rgb="00FFFFFF"/>
+      <x:rgbColor rgb="00FF0000"/>
+      <x:rgbColor rgb="0000FF00"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00800000"/>
+      <x:rgbColor rgb="00008000"/>
+      <x:rgbColor rgb="00000080"/>
+      <x:rgbColor rgb="00808000"/>
+      <x:rgbColor rgb="00800080"/>
+      <x:rgbColor rgb="00008080"/>
+      <x:rgbColor rgb="00C0C0C0"/>
+      <x:rgbColor rgb="00808080"/>
+      <x:rgbColor rgb="009999FF"/>
+      <x:rgbColor rgb="00993366"/>
+      <x:rgbColor rgb="00FFFFCC"/>
+      <x:rgbColor rgb="00CCFFFF"/>
+      <x:rgbColor rgb="00660066"/>
+      <x:rgbColor rgb="00FF8080"/>
+      <x:rgbColor rgb="000066CC"/>
+      <x:rgbColor rgb="00CCCCFF"/>
+      <x:rgbColor rgb="00000080"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00800080"/>
+      <x:rgbColor rgb="00800000"/>
+      <x:rgbColor rgb="00008080"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="0000CCFF"/>
+      <x:rgbColor rgb="00CCFFFF"/>
+      <x:rgbColor rgb="00CCFFCC"/>
+      <x:rgbColor rgb="00FFFF99"/>
+      <x:rgbColor rgb="0099CCFF"/>
+      <x:rgbColor rgb="00FF99CC"/>
+      <x:rgbColor rgb="00CC99FF"/>
+      <x:rgbColor rgb="00FFCC99"/>
+      <x:rgbColor rgb="003366FF"/>
+      <x:rgbColor rgb="0033CCCC"/>
+      <x:rgbColor rgb="0099CC00"/>
+      <x:rgbColor rgb="00FFCC00"/>
+      <x:rgbColor rgb="00FF9900"/>
+      <x:rgbColor rgb="00FF6600"/>
+      <x:rgbColor rgb="00666699"/>
+      <x:rgbColor rgb="00969696"/>
+      <x:rgbColor rgb="00003366"/>
+      <x:rgbColor rgb="00339966"/>
+      <x:rgbColor rgb="00003300"/>
+      <x:rgbColor rgb="00333300"/>
+      <x:rgbColor rgb="00993300"/>
+      <x:rgbColor rgb="00993366"/>
+      <x:rgbColor rgb="00333399"/>
+      <x:rgbColor rgb="00333333"/>
+    </x:indexedColors>
+  </x:colors>
+</x:styleSheet>
 </file>
 
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Маржа в бетоне</author>
-  </authors>
-  <commentList>
-    <comment ref="A11" authorId="0" shapeId="0">
-      <text>
-        <t>Даты вносите по возрастанию: формула ищет ближайшую ставку сверху вниз и на неотсортированном списке даст неверный результат.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
+  <xltc:person displayName="Маржа в бетоне" id="{AEFD8B6D-3006-8EB8-7748-5A9D6A3D6C23}"/>
+</xltc:personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -410,7 +425,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -419,13 +434,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -459,17 +474,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -524,101 +528,97 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="70" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Расчёт процентов по ст. 395 ГК РФ</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Заполните жёлтые ячейки. Синим — то, что вводите вы; чёрным — то, что считают формулы. Ничего, кроме жёлтых ячеек, менять не нужно.</t>
+          <t xml:space="preserve">Расчёт процентов по ст. 395 ГК РФ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="62" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Заполните жёлтые ячейки. Синим — то, что вводите вы; чёрным — то, что считают формулы. Ничего, кроме жёлтых ячеек, менять не нужно.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Сумма долга, руб.</t>
+          <t xml:space="preserve">Сумма долга, руб.</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Из претензии. За вычетом авансов и частичных оплат на дату начала расчёта.</t>
+          <t xml:space="preserve">Из претензии. За вычетом авансов и частичных оплат на дату начала расчёта.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Дата начала просрочки</t>
+          <t xml:space="preserve">Дата начала просрочки</t>
         </is>
       </c>
       <c r="B5" s="6" t="n"/>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>День, следующий за последним днём срока оплаты по договору. Если этот последний день пришёлся на нерабочий, срок оплаты по ст. 193 ГК РФ истекает в ближайший следующий рабочий день, и просрочка начинается со дня после него.</t>
+          <t xml:space="preserve">День, следующий за последним днём срока оплаты по договору. Если этот последний день пришёлся на нерабочий, срок оплаты по ст. 193 ГК РФ истекает в ближайший следующий рабочий день, и просрочка начинается со дня после него.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Дата окончания расчёта</t>
+          <t xml:space="preserve">Дата окончания расчёта</t>
         </is>
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Дата претензии или иска. Для требования «по день фактической уплаты» — дата составления документа.</t>
+          <t xml:space="preserve">Дата претензии или иска. Для требования «по день фактической уплаты» — дата составления документа.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Ключевая ставка Банка России</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Заполните с сайта Банка России cbr.ru, раздел «Ключевая ставка Банка России». Внесите ставку, действовавшую на дату начала просрочки, и все её изменения, попадающие в период расчёта. Значений здесь нет намеренно: ставка меняется, а скачанный файл не обновляется.</t>
+          <t xml:space="preserve">Ключевая ставка Банка России</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="72" customHeight="1">
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Заполните с сайта Банка России cbr.ru, раздел «Ключевая ставка Банка России». Внесите ставку, действовавшую на дату начала просрочки, и все её изменения, попадающие в период расчёта. Значений здесь нет намеренно: ставка меняется, а скачанный файл не обновляется.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Действует с</t>
+          <t xml:space="preserve">Действует с</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Ставка, % годовых</t>
+          <t xml:space="preserve">Ставка, % годовых</t>
         </is>
       </c>
     </row>
@@ -705,19 +705,19 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Частичные оплаты</t>
+          <t xml:space="preserve">Частичные оплаты</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Дата</t>
+          <t xml:space="preserve">Дата</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Сумма, руб.</t>
+          <t xml:space="preserve">Сумма, руб.</t>
         </is>
       </c>
     </row>
@@ -764,1718 +764,1474 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Предупреждение о частичных оплатах</t>
+          <t xml:space="preserve">Предупреждение о частичных оплатах</t>
         </is>
       </c>
     </row>
     <row r="47" ht="64" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Частичная оплата по ст. 319 ГК РФ гасит сначала издержки, затем проценты и только потом основной долг. Отступить от этой очерёдности можно соглашением сторон; одностороннее указание в платёжном поручении соглашением не является и очерёдность не меняет. Порядок такой: есть допустимое соглашение — считайте по нему; соглашения нет — по ст. 319 ГК РФ. Если однородных обязательств несколько, выбор погашаемого — отдельный вопрос, и его решают не здесь. Эта таблица уменьшает базу долга со дня, следующего за датой оплаты: день оплаты остаётся днём просрочки на прежнюю сумму. Это простой вариант; если очерёдность имеет значение для вашего спора, расчёт надо корректировать с юристом.</t>
+          <t xml:space="preserve">Частичная оплата по ст. 319 ГК РФ гасит сначала издержки, затем проценты и только потом основной долг. Отступить от этой очерёдности можно соглашением сторон; одностороннее указание в платёжном поручении соглашением не является и очерёдность не меняет. Порядок такой: есть допустимое соглашение — считайте по нему; соглашения нет — по ст. 319 ГК РФ. Если однородных обязательств несколько, выбор погашаемого — отдельный вопрос, и его решают не здесь. Эта таблица уменьшает базу долга со дня, следующего за датой оплаты: день оплаты остаётся днём просрочки на прежнюю сумму. Это простой вариант; если очерёдность имеет значение для вашего спора, расчёт надо корректировать с юристом.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A47:C47"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+  <legacyDrawing ns1:id="Re0ad01086db143b0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="46" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Одна строка — один период, в котором неизменны и ставка, и база долга</t>
+          <t xml:space="preserve">Одна строка — один период, в котором неизменны и ставка, и база долга</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Заполняются только жёлтые колонки A и B: разбейте срок просрочки по датам смены ставки и по датам частичных оплат. Остальное считается само. Колонка «Проверка» подскажет, если период разбит неверно.</t>
+          <t xml:space="preserve">Заполняются только жёлтые колонки A и B: разбейте срок просрочки по датам смены ставки и по датам частичных оплат. Остальное считается само. Колонка «Проверка» подскажет, если период разбит неверно.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Начало периода</t>
+          <t xml:space="preserve">Начало периода</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>Конец периода</t>
+          <t xml:space="preserve">Конец периода</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Дней в периоде</t>
+          <t xml:space="preserve">Дней в периоде</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>База долга, руб.</t>
+          <t xml:space="preserve">База долга, руб.</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>Ставка, % годовых</t>
+          <t xml:space="preserve">Ставка, % годовых</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>Дней в году</t>
+          <t xml:space="preserve">Дней в году</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>Проценты за период, руб.</t>
+          <t xml:space="preserve">Проценты за период, руб.</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>Проверка</t>
+          <t xml:space="preserve">Проверка</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n"/>
       <c r="B4" s="6" t="n"/>
-      <c r="C4" s="10">
+      <c r="C4" s="10" t="str">
         <f>IF(OR($A4="",$B4=""),"",$B4-$A4+1)</f>
-        <v/>
-      </c>
-      <c r="D4" s="11">
+      </c>
+      <c r="D4" s="11" t="str">
         <f>IF($A4="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A4,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E4" s="12">
+      </c>
+      <c r="E4" s="12" t="str">
         <f>IF($A4="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A4,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F4" s="10">
+      </c>
+      <c r="F4" s="10" t="str">
         <f>IF($A4="","",IF(DAY(DATE(YEAR($A4),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G4" s="11">
+      </c>
+      <c r="G4" s="11" t="str">
         <f>IF(OR($A4="",$E4="",$C4=""),"",ROUND($D4*$E4/100*$C4/$F4,2))</f>
-        <v/>
-      </c>
-      <c r="H4" s="13">
+      </c>
+      <c r="H4" s="13" t="str">
         <f>IF($A4="","",IF(YEAR($A4)&lt;&gt;YEAR($B4),"Период пересекает 31 декабря — разбейте на две строки",IF($B4&lt;$A4,"Конец периода раньше начала",IF($A4&lt;&gt;'Входные данные'!$B$5,"Период пропущен или перекрыт — исправьте даты",IF($E4="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
       <c r="B5" s="6" t="n"/>
-      <c r="C5" s="10">
+      <c r="C5" s="10" t="str">
         <f>IF(OR($A5="",$B5=""),"",$B5-$A5+1)</f>
-        <v/>
-      </c>
-      <c r="D5" s="11">
+      </c>
+      <c r="D5" s="11" t="str">
         <f>IF($A5="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A5,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E5" s="12">
+      </c>
+      <c r="E5" s="12" t="str">
         <f>IF($A5="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A5,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F5" s="10">
+      </c>
+      <c r="F5" s="10" t="str">
         <f>IF($A5="","",IF(DAY(DATE(YEAR($A5),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G5" s="11">
+      </c>
+      <c r="G5" s="11" t="str">
         <f>IF(OR($A5="",$E5="",$C5=""),"",ROUND($D5*$E5/100*$C5/$F5,2))</f>
-        <v/>
-      </c>
-      <c r="H5" s="13">
+      </c>
+      <c r="H5" s="13" t="str">
         <f>IF($A5="","",IF(YEAR($A5)&lt;&gt;YEAR($B5),"Период пересекает 31 декабря — разбейте на две строки",IF($B5&lt;$A5,"Конец периода раньше начала",IF(OR($B4="",$A5&lt;&gt;$B4+1),"Период пропущен или перекрыт — исправьте даты",IF($E5="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n"/>
       <c r="B6" s="6" t="n"/>
-      <c r="C6" s="10">
+      <c r="C6" s="10" t="str">
         <f>IF(OR($A6="",$B6=""),"",$B6-$A6+1)</f>
-        <v/>
-      </c>
-      <c r="D6" s="11">
+      </c>
+      <c r="D6" s="11" t="str">
         <f>IF($A6="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A6,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E6" s="12">
+      </c>
+      <c r="E6" s="12" t="str">
         <f>IF($A6="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A6,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F6" s="10">
+      </c>
+      <c r="F6" s="10" t="str">
         <f>IF($A6="","",IF(DAY(DATE(YEAR($A6),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G6" s="11">
+      </c>
+      <c r="G6" s="11" t="str">
         <f>IF(OR($A6="",$E6="",$C6=""),"",ROUND($D6*$E6/100*$C6/$F6,2))</f>
-        <v/>
-      </c>
-      <c r="H6" s="13">
+      </c>
+      <c r="H6" s="13" t="str">
         <f>IF($A6="","",IF(YEAR($A6)&lt;&gt;YEAR($B6),"Период пересекает 31 декабря — разбейте на две строки",IF($B6&lt;$A6,"Конец периода раньше начала",IF(OR($B5="",$A6&lt;&gt;$B5+1),"Период пропущен или перекрыт — исправьте даты",IF($E6="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
       <c r="B7" s="6" t="n"/>
-      <c r="C7" s="10">
+      <c r="C7" s="10" t="str">
         <f>IF(OR($A7="",$B7=""),"",$B7-$A7+1)</f>
-        <v/>
-      </c>
-      <c r="D7" s="11">
+      </c>
+      <c r="D7" s="11" t="str">
         <f>IF($A7="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A7,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E7" s="12">
+      </c>
+      <c r="E7" s="12" t="str">
         <f>IF($A7="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A7,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F7" s="10">
+      </c>
+      <c r="F7" s="10" t="str">
         <f>IF($A7="","",IF(DAY(DATE(YEAR($A7),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G7" s="11">
+      </c>
+      <c r="G7" s="11" t="str">
         <f>IF(OR($A7="",$E7="",$C7=""),"",ROUND($D7*$E7/100*$C7/$F7,2))</f>
-        <v/>
-      </c>
-      <c r="H7" s="13">
+      </c>
+      <c r="H7" s="13" t="str">
         <f>IF($A7="","",IF(YEAR($A7)&lt;&gt;YEAR($B7),"Период пересекает 31 декабря — разбейте на две строки",IF($B7&lt;$A7,"Конец периода раньше начала",IF(OR($B6="",$A7&lt;&gt;$B6+1),"Период пропущен или перекрыт — исправьте даты",IF($E7="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="10">
+      <c r="C8" s="10" t="str">
         <f>IF(OR($A8="",$B8=""),"",$B8-$A8+1)</f>
-        <v/>
-      </c>
-      <c r="D8" s="11">
+      </c>
+      <c r="D8" s="11" t="str">
         <f>IF($A8="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A8,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E8" s="12">
+      </c>
+      <c r="E8" s="12" t="str">
         <f>IF($A8="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A8,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F8" s="10">
+      </c>
+      <c r="F8" s="10" t="str">
         <f>IF($A8="","",IF(DAY(DATE(YEAR($A8),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G8" s="11">
+      </c>
+      <c r="G8" s="11" t="str">
         <f>IF(OR($A8="",$E8="",$C8=""),"",ROUND($D8*$E8/100*$C8/$F8,2))</f>
-        <v/>
-      </c>
-      <c r="H8" s="13">
+      </c>
+      <c r="H8" s="13" t="str">
         <f>IF($A8="","",IF(YEAR($A8)&lt;&gt;YEAR($B8),"Период пересекает 31 декабря — разбейте на две строки",IF($B8&lt;$A8,"Конец периода раньше начала",IF(OR($B7="",$A8&lt;&gt;$B7+1),"Период пропущен или перекрыт — исправьте даты",IF($E8="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
       <c r="B9" s="6" t="n"/>
-      <c r="C9" s="10">
+      <c r="C9" s="10" t="str">
         <f>IF(OR($A9="",$B9=""),"",$B9-$A9+1)</f>
-        <v/>
-      </c>
-      <c r="D9" s="11">
+      </c>
+      <c r="D9" s="11" t="str">
         <f>IF($A9="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A9,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E9" s="12">
+      </c>
+      <c r="E9" s="12" t="str">
         <f>IF($A9="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A9,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F9" s="10">
+      </c>
+      <c r="F9" s="10" t="str">
         <f>IF($A9="","",IF(DAY(DATE(YEAR($A9),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G9" s="11">
+      </c>
+      <c r="G9" s="11" t="str">
         <f>IF(OR($A9="",$E9="",$C9=""),"",ROUND($D9*$E9/100*$C9/$F9,2))</f>
-        <v/>
-      </c>
-      <c r="H9" s="13">
+      </c>
+      <c r="H9" s="13" t="str">
         <f>IF($A9="","",IF(YEAR($A9)&lt;&gt;YEAR($B9),"Период пересекает 31 декабря — разбейте на две строки",IF($B9&lt;$A9,"Конец периода раньше начала",IF(OR($B8="",$A9&lt;&gt;$B8+1),"Период пропущен или перекрыт — исправьте даты",IF($E9="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="10">
+      <c r="C10" s="10" t="str">
         <f>IF(OR($A10="",$B10=""),"",$B10-$A10+1)</f>
-        <v/>
-      </c>
-      <c r="D10" s="11">
+      </c>
+      <c r="D10" s="11" t="str">
         <f>IF($A10="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A10,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E10" s="12">
+      </c>
+      <c r="E10" s="12" t="str">
         <f>IF($A10="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A10,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F10" s="10">
+      </c>
+      <c r="F10" s="10" t="str">
         <f>IF($A10="","",IF(DAY(DATE(YEAR($A10),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G10" s="11">
+      </c>
+      <c r="G10" s="11" t="str">
         <f>IF(OR($A10="",$E10="",$C10=""),"",ROUND($D10*$E10/100*$C10/$F10,2))</f>
-        <v/>
-      </c>
-      <c r="H10" s="13">
+      </c>
+      <c r="H10" s="13" t="str">
         <f>IF($A10="","",IF(YEAR($A10)&lt;&gt;YEAR($B10),"Период пересекает 31 декабря — разбейте на две строки",IF($B10&lt;$A10,"Конец периода раньше начала",IF(OR($B9="",$A10&lt;&gt;$B9+1),"Период пропущен или перекрыт — исправьте даты",IF($E10="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
       <c r="B11" s="6" t="n"/>
-      <c r="C11" s="10">
+      <c r="C11" s="10" t="str">
         <f>IF(OR($A11="",$B11=""),"",$B11-$A11+1)</f>
-        <v/>
-      </c>
-      <c r="D11" s="11">
+      </c>
+      <c r="D11" s="11" t="str">
         <f>IF($A11="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A11,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E11" s="12">
+      </c>
+      <c r="E11" s="12" t="str">
         <f>IF($A11="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A11,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F11" s="10">
+      </c>
+      <c r="F11" s="10" t="str">
         <f>IF($A11="","",IF(DAY(DATE(YEAR($A11),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G11" s="11">
+      </c>
+      <c r="G11" s="11" t="str">
         <f>IF(OR($A11="",$E11="",$C11=""),"",ROUND($D11*$E11/100*$C11/$F11,2))</f>
-        <v/>
-      </c>
-      <c r="H11" s="13">
+      </c>
+      <c r="H11" s="13" t="str">
         <f>IF($A11="","",IF(YEAR($A11)&lt;&gt;YEAR($B11),"Период пересекает 31 декабря — разбейте на две строки",IF($B11&lt;$A11,"Конец периода раньше начала",IF(OR($B10="",$A11&lt;&gt;$B10+1),"Период пропущен или перекрыт — исправьте даты",IF($E11="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
       <c r="B12" s="6" t="n"/>
-      <c r="C12" s="10">
+      <c r="C12" s="10" t="str">
         <f>IF(OR($A12="",$B12=""),"",$B12-$A12+1)</f>
-        <v/>
-      </c>
-      <c r="D12" s="11">
+      </c>
+      <c r="D12" s="11" t="str">
         <f>IF($A12="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A12,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E12" s="12">
+      </c>
+      <c r="E12" s="12" t="str">
         <f>IF($A12="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A12,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F12" s="10">
+      </c>
+      <c r="F12" s="10" t="str">
         <f>IF($A12="","",IF(DAY(DATE(YEAR($A12),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G12" s="11">
+      </c>
+      <c r="G12" s="11" t="str">
         <f>IF(OR($A12="",$E12="",$C12=""),"",ROUND($D12*$E12/100*$C12/$F12,2))</f>
-        <v/>
-      </c>
-      <c r="H12" s="13">
+      </c>
+      <c r="H12" s="13" t="str">
         <f>IF($A12="","",IF(YEAR($A12)&lt;&gt;YEAR($B12),"Период пересекает 31 декабря — разбейте на две строки",IF($B12&lt;$A12,"Конец периода раньше начала",IF(OR($B11="",$A12&lt;&gt;$B11+1),"Период пропущен или перекрыт — исправьте даты",IF($E12="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
       <c r="B13" s="6" t="n"/>
-      <c r="C13" s="10">
+      <c r="C13" s="10" t="str">
         <f>IF(OR($A13="",$B13=""),"",$B13-$A13+1)</f>
-        <v/>
-      </c>
-      <c r="D13" s="11">
+      </c>
+      <c r="D13" s="11" t="str">
         <f>IF($A13="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A13,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E13" s="12">
+      </c>
+      <c r="E13" s="12" t="str">
         <f>IF($A13="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A13,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F13" s="10">
+      </c>
+      <c r="F13" s="10" t="str">
         <f>IF($A13="","",IF(DAY(DATE(YEAR($A13),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G13" s="11">
+      </c>
+      <c r="G13" s="11" t="str">
         <f>IF(OR($A13="",$E13="",$C13=""),"",ROUND($D13*$E13/100*$C13/$F13,2))</f>
-        <v/>
-      </c>
-      <c r="H13" s="13">
+      </c>
+      <c r="H13" s="13" t="str">
         <f>IF($A13="","",IF(YEAR($A13)&lt;&gt;YEAR($B13),"Период пересекает 31 декабря — разбейте на две строки",IF($B13&lt;$A13,"Конец периода раньше начала",IF(OR($B12="",$A13&lt;&gt;$B12+1),"Период пропущен или перекрыт — исправьте даты",IF($E13="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
       <c r="B14" s="6" t="n"/>
-      <c r="C14" s="10">
+      <c r="C14" s="10" t="str">
         <f>IF(OR($A14="",$B14=""),"",$B14-$A14+1)</f>
-        <v/>
-      </c>
-      <c r="D14" s="11">
+      </c>
+      <c r="D14" s="11" t="str">
         <f>IF($A14="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A14,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E14" s="12">
+      </c>
+      <c r="E14" s="12" t="str">
         <f>IF($A14="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A14,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F14" s="10">
+      </c>
+      <c r="F14" s="10" t="str">
         <f>IF($A14="","",IF(DAY(DATE(YEAR($A14),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G14" s="11">
+      </c>
+      <c r="G14" s="11" t="str">
         <f>IF(OR($A14="",$E14="",$C14=""),"",ROUND($D14*$E14/100*$C14/$F14,2))</f>
-        <v/>
-      </c>
-      <c r="H14" s="13">
+      </c>
+      <c r="H14" s="13" t="str">
         <f>IF($A14="","",IF(YEAR($A14)&lt;&gt;YEAR($B14),"Период пересекает 31 декабря — разбейте на две строки",IF($B14&lt;$A14,"Конец периода раньше начала",IF(OR($B13="",$A14&lt;&gt;$B13+1),"Период пропущен или перекрыт — исправьте даты",IF($E14="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
       <c r="B15" s="6" t="n"/>
-      <c r="C15" s="10">
+      <c r="C15" s="10" t="str">
         <f>IF(OR($A15="",$B15=""),"",$B15-$A15+1)</f>
-        <v/>
-      </c>
-      <c r="D15" s="11">
+      </c>
+      <c r="D15" s="11" t="str">
         <f>IF($A15="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A15,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E15" s="12">
+      </c>
+      <c r="E15" s="12" t="str">
         <f>IF($A15="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A15,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F15" s="10">
+      </c>
+      <c r="F15" s="10" t="str">
         <f>IF($A15="","",IF(DAY(DATE(YEAR($A15),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G15" s="11">
+      </c>
+      <c r="G15" s="11" t="str">
         <f>IF(OR($A15="",$E15="",$C15=""),"",ROUND($D15*$E15/100*$C15/$F15,2))</f>
-        <v/>
-      </c>
-      <c r="H15" s="13">
+      </c>
+      <c r="H15" s="13" t="str">
         <f>IF($A15="","",IF(YEAR($A15)&lt;&gt;YEAR($B15),"Период пересекает 31 декабря — разбейте на две строки",IF($B15&lt;$A15,"Конец периода раньше начала",IF(OR($B14="",$A15&lt;&gt;$B14+1),"Период пропущен или перекрыт — исправьте даты",IF($E15="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="6" t="n"/>
-      <c r="C16" s="10">
+      <c r="C16" s="10" t="str">
         <f>IF(OR($A16="",$B16=""),"",$B16-$A16+1)</f>
-        <v/>
-      </c>
-      <c r="D16" s="11">
+      </c>
+      <c r="D16" s="11" t="str">
         <f>IF($A16="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A16,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E16" s="12">
+      </c>
+      <c r="E16" s="12" t="str">
         <f>IF($A16="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A16,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F16" s="10">
+      </c>
+      <c r="F16" s="10" t="str">
         <f>IF($A16="","",IF(DAY(DATE(YEAR($A16),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G16" s="11">
+      </c>
+      <c r="G16" s="11" t="str">
         <f>IF(OR($A16="",$E16="",$C16=""),"",ROUND($D16*$E16/100*$C16/$F16,2))</f>
-        <v/>
-      </c>
-      <c r="H16" s="13">
+      </c>
+      <c r="H16" s="13" t="str">
         <f>IF($A16="","",IF(YEAR($A16)&lt;&gt;YEAR($B16),"Период пересекает 31 декабря — разбейте на две строки",IF($B16&lt;$A16,"Конец периода раньше начала",IF(OR($B15="",$A16&lt;&gt;$B15+1),"Период пропущен или перекрыт — исправьте даты",IF($E16="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
       <c r="B17" s="6" t="n"/>
-      <c r="C17" s="10">
+      <c r="C17" s="10" t="str">
         <f>IF(OR($A17="",$B17=""),"",$B17-$A17+1)</f>
-        <v/>
-      </c>
-      <c r="D17" s="11">
+      </c>
+      <c r="D17" s="11" t="str">
         <f>IF($A17="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A17,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E17" s="12">
+      </c>
+      <c r="E17" s="12" t="str">
         <f>IF($A17="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A17,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F17" s="10">
+      </c>
+      <c r="F17" s="10" t="str">
         <f>IF($A17="","",IF(DAY(DATE(YEAR($A17),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G17" s="11">
+      </c>
+      <c r="G17" s="11" t="str">
         <f>IF(OR($A17="",$E17="",$C17=""),"",ROUND($D17*$E17/100*$C17/$F17,2))</f>
-        <v/>
-      </c>
-      <c r="H17" s="13">
+      </c>
+      <c r="H17" s="13" t="str">
         <f>IF($A17="","",IF(YEAR($A17)&lt;&gt;YEAR($B17),"Период пересекает 31 декабря — разбейте на две строки",IF($B17&lt;$A17,"Конец периода раньше начала",IF(OR($B16="",$A17&lt;&gt;$B16+1),"Период пропущен или перекрыт — исправьте даты",IF($E17="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
       <c r="B18" s="6" t="n"/>
-      <c r="C18" s="10">
+      <c r="C18" s="10" t="str">
         <f>IF(OR($A18="",$B18=""),"",$B18-$A18+1)</f>
-        <v/>
-      </c>
-      <c r="D18" s="11">
+      </c>
+      <c r="D18" s="11" t="str">
         <f>IF($A18="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A18,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E18" s="12">
+      </c>
+      <c r="E18" s="12" t="str">
         <f>IF($A18="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A18,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F18" s="10">
+      </c>
+      <c r="F18" s="10" t="str">
         <f>IF($A18="","",IF(DAY(DATE(YEAR($A18),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G18" s="11">
+      </c>
+      <c r="G18" s="11" t="str">
         <f>IF(OR($A18="",$E18="",$C18=""),"",ROUND($D18*$E18/100*$C18/$F18,2))</f>
-        <v/>
-      </c>
-      <c r="H18" s="13">
+      </c>
+      <c r="H18" s="13" t="str">
         <f>IF($A18="","",IF(YEAR($A18)&lt;&gt;YEAR($B18),"Период пересекает 31 декабря — разбейте на две строки",IF($B18&lt;$A18,"Конец периода раньше начала",IF(OR($B17="",$A18&lt;&gt;$B17+1),"Период пропущен или перекрыт — исправьте даты",IF($E18="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
       <c r="B19" s="6" t="n"/>
-      <c r="C19" s="10">
+      <c r="C19" s="10" t="str">
         <f>IF(OR($A19="",$B19=""),"",$B19-$A19+1)</f>
-        <v/>
-      </c>
-      <c r="D19" s="11">
+      </c>
+      <c r="D19" s="11" t="str">
         <f>IF($A19="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A19,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E19" s="12">
+      </c>
+      <c r="E19" s="12" t="str">
         <f>IF($A19="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A19,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F19" s="10">
+      </c>
+      <c r="F19" s="10" t="str">
         <f>IF($A19="","",IF(DAY(DATE(YEAR($A19),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G19" s="11">
+      </c>
+      <c r="G19" s="11" t="str">
         <f>IF(OR($A19="",$E19="",$C19=""),"",ROUND($D19*$E19/100*$C19/$F19,2))</f>
-        <v/>
-      </c>
-      <c r="H19" s="13">
+      </c>
+      <c r="H19" s="13" t="str">
         <f>IF($A19="","",IF(YEAR($A19)&lt;&gt;YEAR($B19),"Период пересекает 31 декабря — разбейте на две строки",IF($B19&lt;$A19,"Конец периода раньше начала",IF(OR($B18="",$A19&lt;&gt;$B18+1),"Период пропущен или перекрыт — исправьте даты",IF($E19="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
       <c r="B20" s="6" t="n"/>
-      <c r="C20" s="10">
+      <c r="C20" s="10" t="str">
         <f>IF(OR($A20="",$B20=""),"",$B20-$A20+1)</f>
-        <v/>
-      </c>
-      <c r="D20" s="11">
+      </c>
+      <c r="D20" s="11" t="str">
         <f>IF($A20="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A20,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E20" s="12">
+      </c>
+      <c r="E20" s="12" t="str">
         <f>IF($A20="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A20,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F20" s="10">
+      </c>
+      <c r="F20" s="10" t="str">
         <f>IF($A20="","",IF(DAY(DATE(YEAR($A20),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G20" s="11">
+      </c>
+      <c r="G20" s="11" t="str">
         <f>IF(OR($A20="",$E20="",$C20=""),"",ROUND($D20*$E20/100*$C20/$F20,2))</f>
-        <v/>
-      </c>
-      <c r="H20" s="13">
+      </c>
+      <c r="H20" s="13" t="str">
         <f>IF($A20="","",IF(YEAR($A20)&lt;&gt;YEAR($B20),"Период пересекает 31 декабря — разбейте на две строки",IF($B20&lt;$A20,"Конец периода раньше начала",IF(OR($B19="",$A20&lt;&gt;$B19+1),"Период пропущен или перекрыт — исправьте даты",IF($E20="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
       <c r="B21" s="6" t="n"/>
-      <c r="C21" s="10">
+      <c r="C21" s="10" t="str">
         <f>IF(OR($A21="",$B21=""),"",$B21-$A21+1)</f>
-        <v/>
-      </c>
-      <c r="D21" s="11">
+      </c>
+      <c r="D21" s="11" t="str">
         <f>IF($A21="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A21,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E21" s="12">
+      </c>
+      <c r="E21" s="12" t="str">
         <f>IF($A21="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A21,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F21" s="10">
+      </c>
+      <c r="F21" s="10" t="str">
         <f>IF($A21="","",IF(DAY(DATE(YEAR($A21),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G21" s="11">
+      </c>
+      <c r="G21" s="11" t="str">
         <f>IF(OR($A21="",$E21="",$C21=""),"",ROUND($D21*$E21/100*$C21/$F21,2))</f>
-        <v/>
-      </c>
-      <c r="H21" s="13">
+      </c>
+      <c r="H21" s="13" t="str">
         <f>IF($A21="","",IF(YEAR($A21)&lt;&gt;YEAR($B21),"Период пересекает 31 декабря — разбейте на две строки",IF($B21&lt;$A21,"Конец периода раньше начала",IF(OR($B20="",$A21&lt;&gt;$B20+1),"Период пропущен или перекрыт — исправьте даты",IF($E21="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
       <c r="B22" s="6" t="n"/>
-      <c r="C22" s="10">
+      <c r="C22" s="10" t="str">
         <f>IF(OR($A22="",$B22=""),"",$B22-$A22+1)</f>
-        <v/>
-      </c>
-      <c r="D22" s="11">
+      </c>
+      <c r="D22" s="11" t="str">
         <f>IF($A22="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A22,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E22" s="12">
+      </c>
+      <c r="E22" s="12" t="str">
         <f>IF($A22="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A22,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F22" s="10">
+      </c>
+      <c r="F22" s="10" t="str">
         <f>IF($A22="","",IF(DAY(DATE(YEAR($A22),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G22" s="11">
+      </c>
+      <c r="G22" s="11" t="str">
         <f>IF(OR($A22="",$E22="",$C22=""),"",ROUND($D22*$E22/100*$C22/$F22,2))</f>
-        <v/>
-      </c>
-      <c r="H22" s="13">
+      </c>
+      <c r="H22" s="13" t="str">
         <f>IF($A22="","",IF(YEAR($A22)&lt;&gt;YEAR($B22),"Период пересекает 31 декабря — разбейте на две строки",IF($B22&lt;$A22,"Конец периода раньше начала",IF(OR($B21="",$A22&lt;&gt;$B21+1),"Период пропущен или перекрыт — исправьте даты",IF($E22="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
       <c r="B23" s="6" t="n"/>
-      <c r="C23" s="10">
+      <c r="C23" s="10" t="str">
         <f>IF(OR($A23="",$B23=""),"",$B23-$A23+1)</f>
-        <v/>
-      </c>
-      <c r="D23" s="11">
+      </c>
+      <c r="D23" s="11" t="str">
         <f>IF($A23="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A23,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E23" s="12">
+      </c>
+      <c r="E23" s="12" t="str">
         <f>IF($A23="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A23,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F23" s="10">
+      </c>
+      <c r="F23" s="10" t="str">
         <f>IF($A23="","",IF(DAY(DATE(YEAR($A23),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G23" s="11">
+      </c>
+      <c r="G23" s="11" t="str">
         <f>IF(OR($A23="",$E23="",$C23=""),"",ROUND($D23*$E23/100*$C23/$F23,2))</f>
-        <v/>
-      </c>
-      <c r="H23" s="13">
+      </c>
+      <c r="H23" s="13" t="str">
         <f>IF($A23="","",IF(YEAR($A23)&lt;&gt;YEAR($B23),"Период пересекает 31 декабря — разбейте на две строки",IF($B23&lt;$A23,"Конец периода раньше начала",IF(OR($B22="",$A23&lt;&gt;$B22+1),"Период пропущен или перекрыт — исправьте даты",IF($E23="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
       <c r="B24" s="6" t="n"/>
-      <c r="C24" s="10">
+      <c r="C24" s="10" t="str">
         <f>IF(OR($A24="",$B24=""),"",$B24-$A24+1)</f>
-        <v/>
-      </c>
-      <c r="D24" s="11">
+      </c>
+      <c r="D24" s="11" t="str">
         <f>IF($A24="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A24,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E24" s="12">
+      </c>
+      <c r="E24" s="12" t="str">
         <f>IF($A24="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A24,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F24" s="10">
+      </c>
+      <c r="F24" s="10" t="str">
         <f>IF($A24="","",IF(DAY(DATE(YEAR($A24),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G24" s="11">
+      </c>
+      <c r="G24" s="11" t="str">
         <f>IF(OR($A24="",$E24="",$C24=""),"",ROUND($D24*$E24/100*$C24/$F24,2))</f>
-        <v/>
-      </c>
-      <c r="H24" s="13">
+      </c>
+      <c r="H24" s="13" t="str">
         <f>IF($A24="","",IF(YEAR($A24)&lt;&gt;YEAR($B24),"Период пересекает 31 декабря — разбейте на две строки",IF($B24&lt;$A24,"Конец периода раньше начала",IF(OR($B23="",$A24&lt;&gt;$B23+1),"Период пропущен или перекрыт — исправьте даты",IF($E24="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
       <c r="B25" s="6" t="n"/>
-      <c r="C25" s="10">
+      <c r="C25" s="10" t="str">
         <f>IF(OR($A25="",$B25=""),"",$B25-$A25+1)</f>
-        <v/>
-      </c>
-      <c r="D25" s="11">
+      </c>
+      <c r="D25" s="11" t="str">
         <f>IF($A25="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A25,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E25" s="12">
+      </c>
+      <c r="E25" s="12" t="str">
         <f>IF($A25="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A25,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F25" s="10">
+      </c>
+      <c r="F25" s="10" t="str">
         <f>IF($A25="","",IF(DAY(DATE(YEAR($A25),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G25" s="11">
+      </c>
+      <c r="G25" s="11" t="str">
         <f>IF(OR($A25="",$E25="",$C25=""),"",ROUND($D25*$E25/100*$C25/$F25,2))</f>
-        <v/>
-      </c>
-      <c r="H25" s="13">
+      </c>
+      <c r="H25" s="13" t="str">
         <f>IF($A25="","",IF(YEAR($A25)&lt;&gt;YEAR($B25),"Период пересекает 31 декабря — разбейте на две строки",IF($B25&lt;$A25,"Конец периода раньше начала",IF(OR($B24="",$A25&lt;&gt;$B24+1),"Период пропущен или перекрыт — исправьте даты",IF($E25="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
       <c r="B26" s="6" t="n"/>
-      <c r="C26" s="10">
+      <c r="C26" s="10" t="str">
         <f>IF(OR($A26="",$B26=""),"",$B26-$A26+1)</f>
-        <v/>
-      </c>
-      <c r="D26" s="11">
+      </c>
+      <c r="D26" s="11" t="str">
         <f>IF($A26="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A26,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E26" s="12">
+      </c>
+      <c r="E26" s="12" t="str">
         <f>IF($A26="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A26,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F26" s="10">
+      </c>
+      <c r="F26" s="10" t="str">
         <f>IF($A26="","",IF(DAY(DATE(YEAR($A26),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G26" s="11">
+      </c>
+      <c r="G26" s="11" t="str">
         <f>IF(OR($A26="",$E26="",$C26=""),"",ROUND($D26*$E26/100*$C26/$F26,2))</f>
-        <v/>
-      </c>
-      <c r="H26" s="13">
+      </c>
+      <c r="H26" s="13" t="str">
         <f>IF($A26="","",IF(YEAR($A26)&lt;&gt;YEAR($B26),"Период пересекает 31 декабря — разбейте на две строки",IF($B26&lt;$A26,"Конец периода раньше начала",IF(OR($B25="",$A26&lt;&gt;$B25+1),"Период пропущен или перекрыт — исправьте даты",IF($E26="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
       <c r="B27" s="6" t="n"/>
-      <c r="C27" s="10">
+      <c r="C27" s="10" t="str">
         <f>IF(OR($A27="",$B27=""),"",$B27-$A27+1)</f>
-        <v/>
-      </c>
-      <c r="D27" s="11">
+      </c>
+      <c r="D27" s="11" t="str">
         <f>IF($A27="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A27,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E27" s="12">
+      </c>
+      <c r="E27" s="12" t="str">
         <f>IF($A27="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A27,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F27" s="10">
+      </c>
+      <c r="F27" s="10" t="str">
         <f>IF($A27="","",IF(DAY(DATE(YEAR($A27),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G27" s="11">
+      </c>
+      <c r="G27" s="11" t="str">
         <f>IF(OR($A27="",$E27="",$C27=""),"",ROUND($D27*$E27/100*$C27/$F27,2))</f>
-        <v/>
-      </c>
-      <c r="H27" s="13">
+      </c>
+      <c r="H27" s="13" t="str">
         <f>IF($A27="","",IF(YEAR($A27)&lt;&gt;YEAR($B27),"Период пересекает 31 декабря — разбейте на две строки",IF($B27&lt;$A27,"Конец периода раньше начала",IF(OR($B26="",$A27&lt;&gt;$B26+1),"Период пропущен или перекрыт — исправьте даты",IF($E27="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
       <c r="B28" s="6" t="n"/>
-      <c r="C28" s="10">
+      <c r="C28" s="10" t="str">
         <f>IF(OR($A28="",$B28=""),"",$B28-$A28+1)</f>
-        <v/>
-      </c>
-      <c r="D28" s="11">
+      </c>
+      <c r="D28" s="11" t="str">
         <f>IF($A28="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A28,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E28" s="12">
+      </c>
+      <c r="E28" s="12" t="str">
         <f>IF($A28="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A28,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F28" s="10">
+      </c>
+      <c r="F28" s="10" t="str">
         <f>IF($A28="","",IF(DAY(DATE(YEAR($A28),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G28" s="11">
+      </c>
+      <c r="G28" s="11" t="str">
         <f>IF(OR($A28="",$E28="",$C28=""),"",ROUND($D28*$E28/100*$C28/$F28,2))</f>
-        <v/>
-      </c>
-      <c r="H28" s="13">
+      </c>
+      <c r="H28" s="13" t="str">
         <f>IF($A28="","",IF(YEAR($A28)&lt;&gt;YEAR($B28),"Период пересекает 31 декабря — разбейте на две строки",IF($B28&lt;$A28,"Конец периода раньше начала",IF(OR($B27="",$A28&lt;&gt;$B27+1),"Период пропущен или перекрыт — исправьте даты",IF($E28="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
       <c r="B29" s="6" t="n"/>
-      <c r="C29" s="10">
+      <c r="C29" s="10" t="str">
         <f>IF(OR($A29="",$B29=""),"",$B29-$A29+1)</f>
-        <v/>
-      </c>
-      <c r="D29" s="11">
+      </c>
+      <c r="D29" s="11" t="str">
         <f>IF($A29="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A29,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E29" s="12">
+      </c>
+      <c r="E29" s="12" t="str">
         <f>IF($A29="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A29,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F29" s="10">
+      </c>
+      <c r="F29" s="10" t="str">
         <f>IF($A29="","",IF(DAY(DATE(YEAR($A29),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G29" s="11">
+      </c>
+      <c r="G29" s="11" t="str">
         <f>IF(OR($A29="",$E29="",$C29=""),"",ROUND($D29*$E29/100*$C29/$F29,2))</f>
-        <v/>
-      </c>
-      <c r="H29" s="13">
+      </c>
+      <c r="H29" s="13" t="str">
         <f>IF($A29="","",IF(YEAR($A29)&lt;&gt;YEAR($B29),"Период пересекает 31 декабря — разбейте на две строки",IF($B29&lt;$A29,"Конец периода раньше начала",IF(OR($B28="",$A29&lt;&gt;$B28+1),"Период пропущен или перекрыт — исправьте даты",IF($E29="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
       <c r="B30" s="6" t="n"/>
-      <c r="C30" s="10">
+      <c r="C30" s="10" t="str">
         <f>IF(OR($A30="",$B30=""),"",$B30-$A30+1)</f>
-        <v/>
-      </c>
-      <c r="D30" s="11">
+      </c>
+      <c r="D30" s="11" t="str">
         <f>IF($A30="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A30,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E30" s="12">
+      </c>
+      <c r="E30" s="12" t="str">
         <f>IF($A30="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A30,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F30" s="10">
+      </c>
+      <c r="F30" s="10" t="str">
         <f>IF($A30="","",IF(DAY(DATE(YEAR($A30),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G30" s="11">
+      </c>
+      <c r="G30" s="11" t="str">
         <f>IF(OR($A30="",$E30="",$C30=""),"",ROUND($D30*$E30/100*$C30/$F30,2))</f>
-        <v/>
-      </c>
-      <c r="H30" s="13">
+      </c>
+      <c r="H30" s="13" t="str">
         <f>IF($A30="","",IF(YEAR($A30)&lt;&gt;YEAR($B30),"Период пересекает 31 декабря — разбейте на две строки",IF($B30&lt;$A30,"Конец периода раньше начала",IF(OR($B29="",$A30&lt;&gt;$B29+1),"Период пропущен или перекрыт — исправьте даты",IF($E30="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
       <c r="B31" s="6" t="n"/>
-      <c r="C31" s="10">
+      <c r="C31" s="10" t="str">
         <f>IF(OR($A31="",$B31=""),"",$B31-$A31+1)</f>
-        <v/>
-      </c>
-      <c r="D31" s="11">
+      </c>
+      <c r="D31" s="11" t="str">
         <f>IF($A31="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A31,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E31" s="12">
+      </c>
+      <c r="E31" s="12" t="str">
         <f>IF($A31="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A31,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F31" s="10">
+      </c>
+      <c r="F31" s="10" t="str">
         <f>IF($A31="","",IF(DAY(DATE(YEAR($A31),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G31" s="11">
+      </c>
+      <c r="G31" s="11" t="str">
         <f>IF(OR($A31="",$E31="",$C31=""),"",ROUND($D31*$E31/100*$C31/$F31,2))</f>
-        <v/>
-      </c>
-      <c r="H31" s="13">
+      </c>
+      <c r="H31" s="13" t="str">
         <f>IF($A31="","",IF(YEAR($A31)&lt;&gt;YEAR($B31),"Период пересекает 31 декабря — разбейте на две строки",IF($B31&lt;$A31,"Конец периода раньше начала",IF(OR($B30="",$A31&lt;&gt;$B30+1),"Период пропущен или перекрыт — исправьте даты",IF($E31="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
       <c r="B32" s="6" t="n"/>
-      <c r="C32" s="10">
+      <c r="C32" s="10" t="str">
         <f>IF(OR($A32="",$B32=""),"",$B32-$A32+1)</f>
-        <v/>
-      </c>
-      <c r="D32" s="11">
+      </c>
+      <c r="D32" s="11" t="str">
         <f>IF($A32="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A32,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E32" s="12">
+      </c>
+      <c r="E32" s="12" t="str">
         <f>IF($A32="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A32,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F32" s="10">
+      </c>
+      <c r="F32" s="10" t="str">
         <f>IF($A32="","",IF(DAY(DATE(YEAR($A32),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G32" s="11">
+      </c>
+      <c r="G32" s="11" t="str">
         <f>IF(OR($A32="",$E32="",$C32=""),"",ROUND($D32*$E32/100*$C32/$F32,2))</f>
-        <v/>
-      </c>
-      <c r="H32" s="13">
+      </c>
+      <c r="H32" s="13" t="str">
         <f>IF($A32="","",IF(YEAR($A32)&lt;&gt;YEAR($B32),"Период пересекает 31 декабря — разбейте на две строки",IF($B32&lt;$A32,"Конец периода раньше начала",IF(OR($B31="",$A32&lt;&gt;$B31+1),"Период пропущен или перекрыт — исправьте даты",IF($E32="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
       <c r="B33" s="6" t="n"/>
-      <c r="C33" s="10">
+      <c r="C33" s="10" t="str">
         <f>IF(OR($A33="",$B33=""),"",$B33-$A33+1)</f>
-        <v/>
-      </c>
-      <c r="D33" s="11">
+      </c>
+      <c r="D33" s="11" t="str">
         <f>IF($A33="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A33,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E33" s="12">
+      </c>
+      <c r="E33" s="12" t="str">
         <f>IF($A33="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A33,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F33" s="10">
+      </c>
+      <c r="F33" s="10" t="str">
         <f>IF($A33="","",IF(DAY(DATE(YEAR($A33),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G33" s="11">
+      </c>
+      <c r="G33" s="11" t="str">
         <f>IF(OR($A33="",$E33="",$C33=""),"",ROUND($D33*$E33/100*$C33/$F33,2))</f>
-        <v/>
-      </c>
-      <c r="H33" s="13">
+      </c>
+      <c r="H33" s="13" t="str">
         <f>IF($A33="","",IF(YEAR($A33)&lt;&gt;YEAR($B33),"Период пересекает 31 декабря — разбейте на две строки",IF($B33&lt;$A33,"Конец периода раньше начала",IF(OR($B32="",$A33&lt;&gt;$B32+1),"Период пропущен или перекрыт — исправьте даты",IF($E33="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
       <c r="B34" s="6" t="n"/>
-      <c r="C34" s="10">
+      <c r="C34" s="10" t="str">
         <f>IF(OR($A34="",$B34=""),"",$B34-$A34+1)</f>
-        <v/>
-      </c>
-      <c r="D34" s="11">
+      </c>
+      <c r="D34" s="11" t="str">
         <f>IF($A34="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A34,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E34" s="12">
+      </c>
+      <c r="E34" s="12" t="str">
         <f>IF($A34="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A34,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F34" s="10">
+      </c>
+      <c r="F34" s="10" t="str">
         <f>IF($A34="","",IF(DAY(DATE(YEAR($A34),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G34" s="11">
+      </c>
+      <c r="G34" s="11" t="str">
         <f>IF(OR($A34="",$E34="",$C34=""),"",ROUND($D34*$E34/100*$C34/$F34,2))</f>
-        <v/>
-      </c>
-      <c r="H34" s="13">
+      </c>
+      <c r="H34" s="13" t="str">
         <f>IF($A34="","",IF(YEAR($A34)&lt;&gt;YEAR($B34),"Период пересекает 31 декабря — разбейте на две строки",IF($B34&lt;$A34,"Конец периода раньше начала",IF(OR($B33="",$A34&lt;&gt;$B33+1),"Период пропущен или перекрыт — исправьте даты",IF($E34="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
       <c r="B35" s="6" t="n"/>
-      <c r="C35" s="10">
+      <c r="C35" s="10" t="str">
         <f>IF(OR($A35="",$B35=""),"",$B35-$A35+1)</f>
-        <v/>
-      </c>
-      <c r="D35" s="11">
+      </c>
+      <c r="D35" s="11" t="str">
         <f>IF($A35="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A35,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E35" s="12">
+      </c>
+      <c r="E35" s="12" t="str">
         <f>IF($A35="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A35,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F35" s="10">
+      </c>
+      <c r="F35" s="10" t="str">
         <f>IF($A35="","",IF(DAY(DATE(YEAR($A35),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G35" s="11">
+      </c>
+      <c r="G35" s="11" t="str">
         <f>IF(OR($A35="",$E35="",$C35=""),"",ROUND($D35*$E35/100*$C35/$F35,2))</f>
-        <v/>
-      </c>
-      <c r="H35" s="13">
+      </c>
+      <c r="H35" s="13" t="str">
         <f>IF($A35="","",IF(YEAR($A35)&lt;&gt;YEAR($B35),"Период пересекает 31 декабря — разбейте на две строки",IF($B35&lt;$A35,"Конец периода раньше начала",IF(OR($B34="",$A35&lt;&gt;$B34+1),"Период пропущен или перекрыт — исправьте даты",IF($E35="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
       <c r="B36" s="6" t="n"/>
-      <c r="C36" s="10">
+      <c r="C36" s="10" t="str">
         <f>IF(OR($A36="",$B36=""),"",$B36-$A36+1)</f>
-        <v/>
-      </c>
-      <c r="D36" s="11">
+      </c>
+      <c r="D36" s="11" t="str">
         <f>IF($A36="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A36,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E36" s="12">
+      </c>
+      <c r="E36" s="12" t="str">
         <f>IF($A36="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A36,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F36" s="10">
+      </c>
+      <c r="F36" s="10" t="str">
         <f>IF($A36="","",IF(DAY(DATE(YEAR($A36),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G36" s="11">
+      </c>
+      <c r="G36" s="11" t="str">
         <f>IF(OR($A36="",$E36="",$C36=""),"",ROUND($D36*$E36/100*$C36/$F36,2))</f>
-        <v/>
-      </c>
-      <c r="H36" s="13">
+      </c>
+      <c r="H36" s="13" t="str">
         <f>IF($A36="","",IF(YEAR($A36)&lt;&gt;YEAR($B36),"Период пересекает 31 декабря — разбейте на две строки",IF($B36&lt;$A36,"Конец периода раньше начала",IF(OR($B35="",$A36&lt;&gt;$B35+1),"Период пропущен или перекрыт — исправьте даты",IF($E36="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
       <c r="B37" s="6" t="n"/>
-      <c r="C37" s="10">
+      <c r="C37" s="10" t="str">
         <f>IF(OR($A37="",$B37=""),"",$B37-$A37+1)</f>
-        <v/>
-      </c>
-      <c r="D37" s="11">
+      </c>
+      <c r="D37" s="11" t="str">
         <f>IF($A37="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A37,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E37" s="12">
+      </c>
+      <c r="E37" s="12" t="str">
         <f>IF($A37="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A37,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F37" s="10">
+      </c>
+      <c r="F37" s="10" t="str">
         <f>IF($A37="","",IF(DAY(DATE(YEAR($A37),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G37" s="11">
+      </c>
+      <c r="G37" s="11" t="str">
         <f>IF(OR($A37="",$E37="",$C37=""),"",ROUND($D37*$E37/100*$C37/$F37,2))</f>
-        <v/>
-      </c>
-      <c r="H37" s="13">
+      </c>
+      <c r="H37" s="13" t="str">
         <f>IF($A37="","",IF(YEAR($A37)&lt;&gt;YEAR($B37),"Период пересекает 31 декабря — разбейте на две строки",IF($B37&lt;$A37,"Конец периода раньше начала",IF(OR($B36="",$A37&lt;&gt;$B36+1),"Период пропущен или перекрыт — исправьте даты",IF($E37="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
       <c r="B38" s="6" t="n"/>
-      <c r="C38" s="10">
+      <c r="C38" s="10" t="str">
         <f>IF(OR($A38="",$B38=""),"",$B38-$A38+1)</f>
-        <v/>
-      </c>
-      <c r="D38" s="11">
+      </c>
+      <c r="D38" s="11" t="str">
         <f>IF($A38="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A38,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E38" s="12">
+      </c>
+      <c r="E38" s="12" t="str">
         <f>IF($A38="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A38,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F38" s="10">
+      </c>
+      <c r="F38" s="10" t="str">
         <f>IF($A38="","",IF(DAY(DATE(YEAR($A38),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G38" s="11">
+      </c>
+      <c r="G38" s="11" t="str">
         <f>IF(OR($A38="",$E38="",$C38=""),"",ROUND($D38*$E38/100*$C38/$F38,2))</f>
-        <v/>
-      </c>
-      <c r="H38" s="13">
+      </c>
+      <c r="H38" s="13" t="str">
         <f>IF($A38="","",IF(YEAR($A38)&lt;&gt;YEAR($B38),"Период пересекает 31 декабря — разбейте на две строки",IF($B38&lt;$A38,"Конец периода раньше начала",IF(OR($B37="",$A38&lt;&gt;$B37+1),"Период пропущен или перекрыт — исправьте даты",IF($E38="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
       <c r="B39" s="6" t="n"/>
-      <c r="C39" s="10">
+      <c r="C39" s="10" t="str">
         <f>IF(OR($A39="",$B39=""),"",$B39-$A39+1)</f>
-        <v/>
-      </c>
-      <c r="D39" s="11">
+      </c>
+      <c r="D39" s="11" t="str">
         <f>IF($A39="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A39,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E39" s="12">
+      </c>
+      <c r="E39" s="12" t="str">
         <f>IF($A39="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A39,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F39" s="10">
+      </c>
+      <c r="F39" s="10" t="str">
         <f>IF($A39="","",IF(DAY(DATE(YEAR($A39),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G39" s="11">
+      </c>
+      <c r="G39" s="11" t="str">
         <f>IF(OR($A39="",$E39="",$C39=""),"",ROUND($D39*$E39/100*$C39/$F39,2))</f>
-        <v/>
-      </c>
-      <c r="H39" s="13">
+      </c>
+      <c r="H39" s="13" t="str">
         <f>IF($A39="","",IF(YEAR($A39)&lt;&gt;YEAR($B39),"Период пересекает 31 декабря — разбейте на две строки",IF($B39&lt;$A39,"Конец периода раньше начала",IF(OR($B38="",$A39&lt;&gt;$B38+1),"Период пропущен или перекрыт — исправьте даты",IF($E39="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
       <c r="B40" s="6" t="n"/>
-      <c r="C40" s="10">
+      <c r="C40" s="10" t="str">
         <f>IF(OR($A40="",$B40=""),"",$B40-$A40+1)</f>
-        <v/>
-      </c>
-      <c r="D40" s="11">
+      </c>
+      <c r="D40" s="11" t="str">
         <f>IF($A40="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A40,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E40" s="12">
+      </c>
+      <c r="E40" s="12" t="str">
         <f>IF($A40="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A40,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F40" s="10">
+      </c>
+      <c r="F40" s="10" t="str">
         <f>IF($A40="","",IF(DAY(DATE(YEAR($A40),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G40" s="11">
+      </c>
+      <c r="G40" s="11" t="str">
         <f>IF(OR($A40="",$E40="",$C40=""),"",ROUND($D40*$E40/100*$C40/$F40,2))</f>
-        <v/>
-      </c>
-      <c r="H40" s="13">
+      </c>
+      <c r="H40" s="13" t="str">
         <f>IF($A40="","",IF(YEAR($A40)&lt;&gt;YEAR($B40),"Период пересекает 31 декабря — разбейте на две строки",IF($B40&lt;$A40,"Конец периода раньше начала",IF(OR($B39="",$A40&lt;&gt;$B39+1),"Период пропущен или перекрыт — исправьте даты",IF($E40="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
       <c r="B41" s="6" t="n"/>
-      <c r="C41" s="10">
+      <c r="C41" s="10" t="str">
         <f>IF(OR($A41="",$B41=""),"",$B41-$A41+1)</f>
-        <v/>
-      </c>
-      <c r="D41" s="11">
+      </c>
+      <c r="D41" s="11" t="str">
         <f>IF($A41="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A41,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E41" s="12">
+      </c>
+      <c r="E41" s="12" t="str">
         <f>IF($A41="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A41,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F41" s="10">
+      </c>
+      <c r="F41" s="10" t="str">
         <f>IF($A41="","",IF(DAY(DATE(YEAR($A41),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G41" s="11">
+      </c>
+      <c r="G41" s="11" t="str">
         <f>IF(OR($A41="",$E41="",$C41=""),"",ROUND($D41*$E41/100*$C41/$F41,2))</f>
-        <v/>
-      </c>
-      <c r="H41" s="13">
+      </c>
+      <c r="H41" s="13" t="str">
         <f>IF($A41="","",IF(YEAR($A41)&lt;&gt;YEAR($B41),"Период пересекает 31 декабря — разбейте на две строки",IF($B41&lt;$A41,"Конец периода раньше начала",IF(OR($B40="",$A41&lt;&gt;$B40+1),"Период пропущен или перекрыт — исправьте даты",IF($E41="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
       <c r="B42" s="6" t="n"/>
-      <c r="C42" s="10">
+      <c r="C42" s="10" t="str">
         <f>IF(OR($A42="",$B42=""),"",$B42-$A42+1)</f>
-        <v/>
-      </c>
-      <c r="D42" s="11">
+      </c>
+      <c r="D42" s="11" t="str">
         <f>IF($A42="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A42,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E42" s="12">
+      </c>
+      <c r="E42" s="12" t="str">
         <f>IF($A42="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A42,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F42" s="10">
+      </c>
+      <c r="F42" s="10" t="str">
         <f>IF($A42="","",IF(DAY(DATE(YEAR($A42),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G42" s="11">
+      </c>
+      <c r="G42" s="11" t="str">
         <f>IF(OR($A42="",$E42="",$C42=""),"",ROUND($D42*$E42/100*$C42/$F42,2))</f>
-        <v/>
-      </c>
-      <c r="H42" s="13">
+      </c>
+      <c r="H42" s="13" t="str">
         <f>IF($A42="","",IF(YEAR($A42)&lt;&gt;YEAR($B42),"Период пересекает 31 декабря — разбейте на две строки",IF($B42&lt;$A42,"Конец периода раньше начала",IF(OR($B41="",$A42&lt;&gt;$B41+1),"Период пропущен или перекрыт — исправьте даты",IF($E42="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
       <c r="B43" s="6" t="n"/>
-      <c r="C43" s="10">
+      <c r="C43" s="10" t="str">
         <f>IF(OR($A43="",$B43=""),"",$B43-$A43+1)</f>
-        <v/>
-      </c>
-      <c r="D43" s="11">
+      </c>
+      <c r="D43" s="11" t="str">
         <f>IF($A43="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A43,'Входные данные'!$B$35:$B$44))</f>
-        <v/>
-      </c>
-      <c r="E43" s="12">
+      </c>
+      <c r="E43" s="12" t="str">
         <f>IF($A43="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A43,'Входные данные'!$A$12:$A$31,1)),""))</f>
-        <v/>
-      </c>
-      <c r="F43" s="10">
+      </c>
+      <c r="F43" s="10" t="str">
         <f>IF($A43="","",IF(DAY(DATE(YEAR($A43),2,29))=29,366,365))</f>
-        <v/>
-      </c>
-      <c r="G43" s="11">
+      </c>
+      <c r="G43" s="11" t="str">
         <f>IF(OR($A43="",$E43="",$C43=""),"",ROUND($D43*$E43/100*$C43/$F43,2))</f>
-        <v/>
-      </c>
-      <c r="H43" s="13">
+      </c>
+      <c r="H43" s="13" t="str">
         <f>IF($A43="","",IF(YEAR($A43)&lt;&gt;YEAR($B43),"Период пересекает 31 декабря — разбейте на две строки",IF($B43&lt;$A43,"Конец периода раньше начала",IF(OR($B42="",$A43&lt;&gt;$B42+1),"Период пропущен или перекрыт — исправьте даты",IF($E43="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
-        <v/>
       </c>
     </row>
     <row r="45">
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>Проценты по ст. 395 ГК РФ, всего:</t>
-        </is>
-      </c>
-      <c r="G45" s="15">
+          <t xml:space="preserve">Проценты по ст. 395 ГК РФ, всего:</t>
+        </is>
+      </c>
+      <c r="G45" s="15" t="n">
         <f>ROUND(SUM($G$4:$G$43),2)</f>
-        <v/>
-      </c>
-      <c r="H45" s="16">
+        <v>0</v>
+      </c>
+      <c r="H45" s="16" t="str">
         <f>IF(COUNT($A$4:$A$43)=0,"",IF(MAX($B$4:$B$43)&lt;&gt;'Входные данные'!$B$6,"Последний период не совпадает с датой окончания",""))</f>
-        <v/>
       </c>
     </row>
     <row r="46">
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>Долг плюс проценты:</t>
-        </is>
-      </c>
-      <c r="G46" s="15">
+          <t xml:space="preserve">Долг плюс проценты:</t>
+        </is>
+      </c>
+      <c r="G46" s="15" t="n">
         <f>ROUND('Входные данные'!$B$4-SUM('Входные данные'!$B$35:$B$44)+$G$45,2)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="48" ht="46" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Число дней в году берётся фактическое — 365 или 366. Формула считает по фактическому числу дней; норму, которая устанавливала бы иной знаменатель, этот расчёт не применяет. Если для вашего спора знаменатель принципиален, сверьте его с юристом по действующей практике на дату расчёта.</t>
+          <t xml:space="preserve">Число дней в году берётся фактическое — 365 или 366. Формула считает по фактическому числу дней; норму, которая устанавливала бы иной знаменатель, этот расчёт не применяет. Если для вашего спора знаменатель принципиален, сверьте его с юристом по действующей практике на дату расчёта.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Проверьте себя перед отправкой</t>
+          <t xml:space="preserve">Проверьте себя перед отправкой</t>
         </is>
       </c>
     </row>
     <row r="51" ht="46" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Сверьте итог с любым публичным калькулятором процентов по ст. 395 ГК РФ — например, в справочно-правовой системе. Расхождение больше копеек на округлении означает ошибку в разбивке периодов, а не в калькуляторе. Колонка «Проверка» должна быть пустой во всех заполненных строках.</t>
+          <t xml:space="preserve">Сверьте итог с любым публичным калькулятором процентов по ст. 395 ГК РФ — например, в справочно-правовой системе. Расхождение больше копеек на округлении означает ошибку в разбивке периодов, а не в калькуляторе. Колонка «Проверка» должна быть пустой во всех заполненных строках.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells>
     <mergeCell ref="A48:H48"/>
     <mergeCell ref="A51:H51"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Готовый блок для претензии или иска</t>
+          <t xml:space="preserve">Готовый блок для претензии или иска</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Значения подставляются сами. Лист печатается как приложение «Расчёт взыскиваемой суммы» — судьи ждут расчёт в разбивке по периодам, поэтому печатайте вместе с листом «Расчёт».</t>
+          <t xml:space="preserve">Значения подставляются сами. Лист печатается как приложение «Расчёт взыскиваемой суммы» — судьи ждут расчёт в разбивке по периодам, поэтому печатайте вместе с листом «Расчёт».</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t>Сумма долга на начало расчёта, руб.</t>
-        </is>
-      </c>
-      <c r="B4" s="18">
+          <t xml:space="preserve">Сумма долга на начало расчёта, руб.</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="n">
         <f>'Входные данные'!$B$4</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
-          <t>Учтено частичных оплат, руб.</t>
-        </is>
-      </c>
-      <c r="B5" s="18">
+          <t xml:space="preserve">Учтено частичных оплат, руб.</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="n">
         <f>ROUND(SUM('Входные данные'!$B$35:$B$44),2)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
         <is>
-          <t>Основной долг к взысканию, руб.</t>
-        </is>
-      </c>
-      <c r="B6" s="18">
+          <t xml:space="preserve">Основной долг к взысканию, руб.</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="n">
         <f>ROUND('Входные данные'!$B$4-SUM('Входные данные'!$B$35:$B$44),2)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
-          <t>Период начисления с</t>
-        </is>
-      </c>
-      <c r="B7" s="19">
+          <t xml:space="preserve">Период начисления с</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="n">
         <f>'Входные данные'!$B$5</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>Период начисления по</t>
-        </is>
-      </c>
-      <c r="B8" s="19">
+          <t xml:space="preserve">Период начисления по</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="n">
         <f>'Входные данные'!$B$6</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>Всего дней просрочки</t>
-        </is>
-      </c>
-      <c r="B9" s="20">
+          <t xml:space="preserve">Всего дней просрочки</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="str">
         <f>IF(OR('Входные данные'!$B$5="",'Входные данные'!$B$6=""),"",'Входные данные'!$B$6-'Входные данные'!$B$5+1)</f>
-        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>Проценты по ст. 395 ГК РФ, руб.</t>
-        </is>
-      </c>
-      <c r="B10" s="18">
+          <t xml:space="preserve">Проценты по ст. 395 ГК РФ, руб.</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="n">
         <f>'Расчёт'!$G$45</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>Итого к взысканию, руб.</t>
-        </is>
-      </c>
-      <c r="B11" s="18">
+          <t xml:space="preserve">Итого к взысканию, руб.</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="n">
         <f>'Расчёт'!$G$46</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Фраза для документа</t>
+          <t xml:space="preserve">Фраза для документа</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="21" t="inlineStr">
         <is>
-          <t>Проценты подлежат начислению по день фактической уплаты долга (п. 3 ст. 395 ГК РФ).</t>
+          <t xml:space="preserve">Проценты подлежат начислению по день фактической уплаты долга (п. 3 ст. 395 ГК РФ).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Что это не заменяет</t>
+          <t xml:space="preserve">Что это не заменяет</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>— Выбор между процентами по ст. 395 и договорной неустойкой. Если договором установлена неустойка за просрочку оплаты, по общему правилу взыскивается она (п. 4 ст. 395 ГК РФ) — выбор согласуйте с юристом.</t>
+          <t xml:space="preserve">— Выбор между процентами по ст. 395 и договорной неустойкой. Если договором установлена неустойка за просрочку оплаты, по общему правилу взыскивается она (п. 4 ст. 395 ГК РФ) — выбор согласуйте с юристом.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>— Учёт мораторных периодов, банкротства должника и иных оснований приостановки начисления. При таких обстоятельствах расчёт корректирует юрист.</t>
+          <t xml:space="preserve">— Учёт мораторных периодов, банкротства должника и иных оснований приостановки начисления. При таких обстоятельствах расчёт корректирует юрист.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="46" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>— Заключение специалиста. Суд проверяет расчёт сам; эта таблица — рабочий инструмент истца, а не доказательство само по себе.</t>
+          <t xml:space="preserve">— Заключение специалиста. Суд проверяет расчёт сам; эта таблица — рабочий инструмент истца, а не доказательство само по себе.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="46" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>— Юридическую консультацию и вычитку юристом. Порядок расчёта сверен с текстом действующих норм 16.08.2026: нормативная сверка сопоставляет формулировки и порядок со статьями закона и правовой позиции по вашему спору не оценивает.</t>
+          <t xml:space="preserve">— Юридическую консультацию и вычитку юристом. Порядок расчёта сверен с текстом действующих норм 16.08.2026: нормативная сверка сопоставляет формулировки и порядок со статьями закона и правовой позиции по вашему спору не оценивает.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A18:B18"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Пример: как выглядят заполненные поля</t>
+          <t xml:space="preserve">Пример: как выглядят заполненные поля</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="22" t="inlineStr">
         <is>
-          <t>Здесь показан формат ввода, а не ваш расчёт. Цифры вымышленные, ставки — условные: реальные берите на cbr.ru. Ничего отсюда не переносите в документ.</t>
+          <t xml:space="preserve">Здесь показан формат ввода, а не ваш расчёт. Цифры вымышленные, ставки — условные: реальные берите на cbr.ru. Ничего отсюда не переносите в документ.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Входные данные</t>
+          <t xml:space="preserve">Входные данные</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="21" t="inlineStr">
         <is>
-          <t>Сумма долга, руб.</t>
+          <t xml:space="preserve">Сумма долга, руб.</t>
         </is>
       </c>
       <c r="B5" s="23" t="inlineStr">
         <is>
-          <t>1 250 000,00</t>
+          <t xml:space="preserve">1 250 000,00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="21" t="inlineStr">
         <is>
-          <t>Дата начала просрочки</t>
+          <t xml:space="preserve">Дата начала просрочки</t>
         </is>
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>15.03.2026</t>
+          <t xml:space="preserve">15.03.2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="21" t="inlineStr">
         <is>
-          <t>Дата окончания расчёта</t>
+          <t xml:space="preserve">Дата окончания расчёта</t>
         </is>
       </c>
       <c r="B7" s="23" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t xml:space="preserve">30.07.2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Таблица ставок</t>
+          <t xml:space="preserve">Таблица ставок</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Действует с</t>
+          <t xml:space="preserve">Действует с</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Ставка, % годовых</t>
+          <t xml:space="preserve">Ставка, % годовых</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>15.03.2026</t>
+          <t xml:space="preserve">15.03.2026</t>
         </is>
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>условная 1</t>
+          <t xml:space="preserve">условная 1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="23" t="inlineStr">
         <is>
-          <t>28.04.2026</t>
+          <t xml:space="preserve">28.04.2026</t>
         </is>
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>условная 2</t>
+          <t xml:space="preserve">условная 2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Строки листа «Расчёт»</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Начало периода</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Конец периода</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Дней в периоде</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>База долга, руб.</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>Ставка, % годовых</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>Дней в году</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>Проценты за период, руб.</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>Проверка</t>
+          <t xml:space="preserve">Строки листа «Расчёт»</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="38" customHeight="1">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Начало периода</t>
+        </is>
+      </c>
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Конец периода</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дней в периоде</t>
+        </is>
+      </c>
+      <c r="D15" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">База долга, руб.</t>
+        </is>
+      </c>
+      <c r="E15" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ставка, % годовых</t>
+        </is>
+      </c>
+      <c r="F15" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дней в году</t>
+        </is>
+      </c>
+      <c r="G15" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Проценты за период, руб.</t>
+        </is>
+      </c>
+      <c r="H15" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Проверка</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>15.03.2026</t>
+          <t xml:space="preserve">15.03.2026</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>27.04.2026</t>
+          <t xml:space="preserve">27.04.2026</t>
         </is>
       </c>
       <c r="C16" s="25" t="inlineStr">
         <is>
-          <t>считается</t>
+          <t xml:space="preserve">считается</t>
         </is>
       </c>
       <c r="D16" s="25" t="inlineStr">
         <is>
-          <t>считается</t>
+          <t xml:space="preserve">считается</t>
         </is>
       </c>
       <c r="E16" s="25" t="inlineStr">
         <is>
-          <t>подставится</t>
+          <t xml:space="preserve">подставится</t>
         </is>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>считается</t>
+          <t xml:space="preserve">считается</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>считается</t>
+          <t xml:space="preserve">считается</t>
         </is>
       </c>
       <c r="H16" s="25" t="inlineStr">
         <is>
-          <t>пусто, если всё верно</t>
+          <t xml:space="preserve">пусто, если всё верно</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>28.04.2026</t>
+          <t xml:space="preserve">28.04.2026</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t xml:space="preserve">30.07.2026</t>
         </is>
       </c>
       <c r="C17" s="25" t="inlineStr">
         <is>
-          <t>считается</t>
+          <t xml:space="preserve">считается</t>
         </is>
       </c>
       <c r="D17" s="25" t="inlineStr">
         <is>
-          <t>считается</t>
+          <t xml:space="preserve">считается</t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr">
         <is>
-          <t>подставится</t>
+          <t xml:space="preserve">подставится</t>
         </is>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>считается</t>
+          <t xml:space="preserve">считается</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>считается</t>
+          <t xml:space="preserve">считается</t>
         </is>
       </c>
       <c r="H17" s="25" t="inlineStr">
         <is>
-          <t>пусто, если всё верно</t>
+          <t xml:space="preserve">пусто, если всё верно</t>
         </is>
       </c>
     </row>
     <row r="19" ht="46" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Обратите внимание: период разбит на две строки по дате смены ставки. Если бы просрочка пересекала 31 декабря, разбить пришлось бы и там — колонка «Проверка» об этом напомнит.</t>
+          <t xml:space="preserve">Обратите внимание: период разбит на две строки по дате смены ставки. Если бы просрочка пересекала 31 декабря, разбить пришлось бы и там — колонка «Проверка» об этом напомнит.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells>
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A2:H2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
--- a/products-storage/04-polnyy-komplekt-pto/01-30-bazovye-pakety/01-zakrytie-rabot/14-raschet-procentov-395-gk.xlsx
+++ b/products-storage/04-polnyy-komplekt-pto/01-30-bazovye-pakety/01-zakrytie-rabot/14-raschet-procentov-395-gk.xlsx
@@ -1,264 +1,251 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Входные данные" sheetId="1" r:id="R8705f6fed4154697"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Расчёт" sheetId="2" r:id="R916296fa190a4036"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Итог для документа" sheetId="3" r:id="Rae5eb32b2f5e4c1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Пример заполнения" sheetId="4" r:id="Rd6a7f6e91e0d4e5a"/>
-  </x:sheets>
-</x:workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:authors>
-    <x:author>Маржа в бетоне</x:author>
-  </x:authors>
-  <x:commentList>
-    <x:comment ref="A11" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>Даты вносите по возрастанию: формула ищет ближайшую ставку сверху вниз и на неотсортированном списке даст неверный результат.</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-  </x:commentList>
-</x:comments>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Входные данные" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Расчёт" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Итог для документа" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Пример заполнения" sheetId="4" state="visible" r:id="rId4"/>
+  </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Итог для документа'!$A$1:$B$19</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
-    <x:numFmt numFmtId="164" formatCode="DD.MM.YYYY"/>
-    <x:numFmt numFmtId="200" formatCode="DD.MM.YYYY;;"/>
-  </x:numFmts>
-  <x:fonts count="10">
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="14"/>
-      <x:name val="Times New Roman"/>
-    </x:font>
-    <x:font>
-      <x:i/>
-      <x:sz val="10"/>
-      <x:color rgb="FF595959"/>
-      <x:name val="Times New Roman"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:name val="Times New Roman"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="Times New Roman"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:name val="Times New Roman"/>
-    </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:color rgb="FFC00000"/>
-      <x:name val="Times New Roman"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="10"/>
-      <x:color rgb="FFC00000"/>
-      <x:name val="Times New Roman"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF008000"/>
-      <x:name val="Times New Roman"/>
-    </x:font>
-    <x:font>
-      <x:i/>
-      <x:sz val="10"/>
-      <x:color rgb="FFC00000"/>
-      <x:name val="Times New Roman"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="4">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFF2CC"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFE7E6E6"/>
-      </x:patternFill>
-    </x:fill>
-  </x:fills>
-  <x:borders count="2">
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFBFBFBF"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFBFBFBF"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFBFBFBF"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFBFBFBF"/>
-      </x:bottom>
-    </x:border>
-  </x:borders>
-  <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </x:cellStyleXfs>
-  <x:cellXfs count="30">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="4" fontId="4" fillId="2" borderId="1" xfId="0"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0"/>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0"/>
-    <x:xf numFmtId="2" fontId="4" fillId="2" borderId="1" xfId="0"/>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0"/>
-    <x:xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0"/>
-    <x:xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0"/>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment horizontal="right"/>
-    </x:xf>
-    <x:xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0"/>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0"/>
-    <x:xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0"/>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0"/>
-    <x:xf numFmtId="1" fontId="8" fillId="0" borderId="1" xfId="0"/>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-  </x:cellXfs>
-  <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0"/>
-  </x:cellStyles>
-  <x:colors>
-    <x:indexedColors>
-      <x:rgbColor rgb="00000000"/>
-      <x:rgbColor rgb="00FFFFFF"/>
-      <x:rgbColor rgb="00FF0000"/>
-      <x:rgbColor rgb="0000FF00"/>
-      <x:rgbColor rgb="000000FF"/>
-      <x:rgbColor rgb="00FFFF00"/>
-      <x:rgbColor rgb="00FF00FF"/>
-      <x:rgbColor rgb="0000FFFF"/>
-      <x:rgbColor rgb="00000000"/>
-      <x:rgbColor rgb="00FFFFFF"/>
-      <x:rgbColor rgb="00FF0000"/>
-      <x:rgbColor rgb="0000FF00"/>
-      <x:rgbColor rgb="000000FF"/>
-      <x:rgbColor rgb="00FFFF00"/>
-      <x:rgbColor rgb="00FF00FF"/>
-      <x:rgbColor rgb="0000FFFF"/>
-      <x:rgbColor rgb="00800000"/>
-      <x:rgbColor rgb="00008000"/>
-      <x:rgbColor rgb="00000080"/>
-      <x:rgbColor rgb="00808000"/>
-      <x:rgbColor rgb="00800080"/>
-      <x:rgbColor rgb="00008080"/>
-      <x:rgbColor rgb="00C0C0C0"/>
-      <x:rgbColor rgb="00808080"/>
-      <x:rgbColor rgb="009999FF"/>
-      <x:rgbColor rgb="00993366"/>
-      <x:rgbColor rgb="00FFFFCC"/>
-      <x:rgbColor rgb="00CCFFFF"/>
-      <x:rgbColor rgb="00660066"/>
-      <x:rgbColor rgb="00FF8080"/>
-      <x:rgbColor rgb="000066CC"/>
-      <x:rgbColor rgb="00CCCCFF"/>
-      <x:rgbColor rgb="00000080"/>
-      <x:rgbColor rgb="00FF00FF"/>
-      <x:rgbColor rgb="00FFFF00"/>
-      <x:rgbColor rgb="0000FFFF"/>
-      <x:rgbColor rgb="00800080"/>
-      <x:rgbColor rgb="00800000"/>
-      <x:rgbColor rgb="00008080"/>
-      <x:rgbColor rgb="000000FF"/>
-      <x:rgbColor rgb="0000CCFF"/>
-      <x:rgbColor rgb="00CCFFFF"/>
-      <x:rgbColor rgb="00CCFFCC"/>
-      <x:rgbColor rgb="00FFFF99"/>
-      <x:rgbColor rgb="0099CCFF"/>
-      <x:rgbColor rgb="00FF99CC"/>
-      <x:rgbColor rgb="00CC99FF"/>
-      <x:rgbColor rgb="00FFCC99"/>
-      <x:rgbColor rgb="003366FF"/>
-      <x:rgbColor rgb="0033CCCC"/>
-      <x:rgbColor rgb="0099CC00"/>
-      <x:rgbColor rgb="00FFCC00"/>
-      <x:rgbColor rgb="00FF9900"/>
-      <x:rgbColor rgb="00FF6600"/>
-      <x:rgbColor rgb="00666699"/>
-      <x:rgbColor rgb="00969696"/>
-      <x:rgbColor rgb="00003366"/>
-      <x:rgbColor rgb="00339966"/>
-      <x:rgbColor rgb="00003300"/>
-      <x:rgbColor rgb="00333300"/>
-      <x:rgbColor rgb="00993300"/>
-      <x:rgbColor rgb="00993366"/>
-      <x:rgbColor rgb="00333399"/>
-      <x:rgbColor rgb="00333333"/>
-    </x:indexedColors>
-  </x:colors>
-</x:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="DD.MM.YYYY"/>
+    <numFmt numFmtId="165" formatCode="DD.MM.YYYY;;"/>
+  </numFmts>
+  <fonts count="8">
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00343638"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00343638"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <color rgb="00343638"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <i val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+  </fonts>
+  <fills count="4">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3EEDF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7E6E6"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="26">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="Маржа в бетоне" id="{AEFD8B6D-3006-8EB8-7748-5A9D6A3D6C23}"/>
-</xltc:personList>
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Маржа в бетоне</author>
+  </authors>
+  <commentList>
+    <comment ref="A11" authorId="0" shapeId="0">
+      <text>
+        <t>Даты вносите по возрастанию: формула ищет ближайшую ставку сверху вниз и на неотсортированном списке даст неверный результат.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -425,7 +412,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -434,13 +421,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -474,6 +461,17 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -528,97 +526,101 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="70" customWidth="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Расчёт процентов по ст. 395 ГК РФ</t>
+          <t>Расчёт процентов по ст. 395 ГК РФ</t>
         </is>
       </c>
     </row>
     <row r="2" ht="62" customHeight="1">
-      <c r="A2" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Заполните жёлтые ячейки. Синим — то, что вводите вы; чёрным — то, что считают формулы. Ничего, кроме жёлтых ячеек, менять не нужно.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Заполните ячейки со светло-золотистой заливкой. Остальные ячейки содержат подписи и формулы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="46" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сумма долга, руб.</t>
+          <t>Сумма долга, руб.</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Из претензии. За вычетом авансов и частичных оплат на дату начала расчёта.</t>
+          <t>Долг на дату начала просрочки, после вычета авансов и оплат до этой даты. Оплаты в периоде расчёта вносите только в таблицу «Частичные оплаты». Остаток для документа берите с листа «Итог для документа».</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дата начала просрочки</t>
+          <t>Дата начала просрочки</t>
         </is>
       </c>
       <c r="B5" s="6" t="n"/>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">День, следующий за последним днём срока оплаты по договору. Если этот последний день пришёлся на нерабочий, срок оплаты по ст. 193 ГК РФ истекает в ближайший следующий рабочий день, и просрочка начинается со дня после него.</t>
+          <t>День, следующий за последним днём срока оплаты по договору. Если этот последний день пришёлся на нерабочий, срок оплаты по ст. 193 ГК РФ истекает в ближайший следующий рабочий день, и просрочка начинается со дня после него.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дата окончания расчёта</t>
+          <t>Дата окончания расчёта</t>
         </is>
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дата претензии или иска. Для требования «по день фактической уплаты» — дата составления документа.</t>
+          <t>Дата претензии или иска. Для требования «по день фактической уплаты» — дата составления документа.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ключевая ставка Банка России</t>
+          <t>Ключевая ставка Банка России</t>
         </is>
       </c>
     </row>
     <row r="9" ht="72" customHeight="1">
-      <c r="A9" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Заполните с сайта Банка России cbr.ru, раздел «Ключевая ставка Банка России». Внесите ставку, действовавшую на дату начала просрочки, и все её изменения, попадающие в период расчёта. Значений здесь нет намеренно: ставка меняется, а скачанный файл не обновляется.</t>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Заполните с сайта Банка России cbr.ru, раздел «Ключевая ставка Банка России». Внесите ставку, действовавшую на дату начала просрочки, и все её изменения, попадающие в период расчёта. Значений здесь нет намеренно: ставка меняется, а скачанный файл не обновляется.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Действует с</t>
+          <t>Действует с</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ставка, % годовых</t>
+          <t>Ставка, % годовых</t>
         </is>
       </c>
     </row>
@@ -705,19 +707,19 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Частичные оплаты</t>
+          <t>Частичные оплаты</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дата</t>
+          <t>Дата</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сумма, руб.</t>
+          <t>Сумма, руб.</t>
         </is>
       </c>
     </row>
@@ -764,1474 +766,1723 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Предупреждение о частичных оплатах</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="64" customHeight="1">
+          <t>Предупреждение о частичных оплатах</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="98" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Частичная оплата по ст. 319 ГК РФ гасит сначала издержки, затем проценты и только потом основной долг. Отступить от этой очерёдности можно соглашением сторон; одностороннее указание в платёжном поручении соглашением не является и очерёдность не меняет. Порядок такой: есть допустимое соглашение — считайте по нему; соглашения нет — по ст. 319 ГК РФ. Если однородных обязательств несколько, выбор погашаемого — отдельный вопрос, и его решают не здесь. Эта таблица уменьшает базу долга со дня, следующего за датой оплаты: день оплаты остаётся днём просрочки на прежнюю сумму. Это простой вариант; если очерёдность имеет значение для вашего спора, расчёт надо корректировать с юристом.</t>
+          <t>В этой таблице учитывайте только сумму оплаты, направленную на погашение основного долга. По ст. 319 ГК РФ при недостаточности платежа сначала погашаются издержки кредитора по получению исполнения и проценты, являющиеся платой за пользование денежными средствами, затем основной долг. Проценты за просрочку по ст. 395 ГК РФ погашаются после основного долга (п. 49 постановления Пленума ВС РФ от 24.03.2016 № 7). Соглашением сторон можно изменить очередность только требований, названных в ст. 319 ГК РФ (п. 37 постановления Пленума ВС РФ от 22.11.2016 № 54). Если платёж распределяется между несколькими обязательствами или включает иные требования, уточните сумму погашения основного долга с юристом. База долга уменьшается со дня, следующего за датой оплаты; в день оплаты проценты начисляются на прежнюю сумму.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="2">
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A47:C47"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
-  <legacyDrawing ns1:id="Re0ad01086db143b0"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="46" customWidth="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Одна строка — один период, в котором неизменны и ставка, и база долга</t>
+          <t>Одна строка — один период, в котором неизменны и ставка, и база долга</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Заполняются только жёлтые колонки A и B: разбейте срок просрочки по датам смены ставки и по датам частичных оплат. Остальное считается само. Колонка «Проверка» подскажет, если период разбит неверно.</t>
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Заполняются только колонки A и B со светло-золотистой заливкой: разбейте срок просрочки по датам смены ставки и по датам частичных оплат. Остальное считается само. Колонка «Проверка» подскажет, если период разбит неверно.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Начало периода</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Конец периода</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Дней в периоде</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">База долга, руб.</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ставка, % годовых</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Дней в году</t>
-        </is>
-      </c>
-      <c r="G3" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Проценты за период, руб.</t>
-        </is>
-      </c>
-      <c r="H3" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Проверка</t>
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Начало периода</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Конец периода</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Дней в периоде</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>База долга, руб.</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Ставка, % годовых</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Дней в году</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>Проценты за период, руб.</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Проверка</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n"/>
       <c r="B4" s="6" t="n"/>
-      <c r="C4" s="10" t="str">
+      <c r="C4" s="11">
         <f>IF(OR($A4="",$B4=""),"",$B4-$A4+1)</f>
-      </c>
-      <c r="D4" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D4" s="12">
         <f>IF($A4="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A4,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E4" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E4" s="13">
         <f>IF($A4="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A4,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F4" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F4" s="11">
         <f>IF($A4="","",IF(DAY(DATE(YEAR($A4),2,29))=29,366,365))</f>
-      </c>
-      <c r="G4" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G4" s="12">
         <f>IF(OR($A4="",$E4="",$C4=""),"",ROUND($D4*$E4/100*$C4/$F4,2))</f>
-      </c>
-      <c r="H4" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H4" s="14">
         <f>IF($A4="","",IF(YEAR($A4)&lt;&gt;YEAR($B4),"Период пересекает 31 декабря — разбейте на две строки",IF($B4&lt;$A4,"Конец периода раньше начала",IF($A4&lt;&gt;'Входные данные'!$B$5,"Период пропущен или перекрыт — исправьте даты",IF($E4="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
       <c r="B5" s="6" t="n"/>
-      <c r="C5" s="10" t="str">
+      <c r="C5" s="11">
         <f>IF(OR($A5="",$B5=""),"",$B5-$A5+1)</f>
-      </c>
-      <c r="D5" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D5" s="12">
         <f>IF($A5="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A5,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E5" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E5" s="13">
         <f>IF($A5="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A5,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F5" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F5" s="11">
         <f>IF($A5="","",IF(DAY(DATE(YEAR($A5),2,29))=29,366,365))</f>
-      </c>
-      <c r="G5" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G5" s="12">
         <f>IF(OR($A5="",$E5="",$C5=""),"",ROUND($D5*$E5/100*$C5/$F5,2))</f>
-      </c>
-      <c r="H5" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H5" s="14">
         <f>IF($A5="","",IF(YEAR($A5)&lt;&gt;YEAR($B5),"Период пересекает 31 декабря — разбейте на две строки",IF($B5&lt;$A5,"Конец периода раньше начала",IF(OR($B4="",$A5&lt;&gt;$B4+1),"Период пропущен или перекрыт — исправьте даты",IF($E5="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n"/>
       <c r="B6" s="6" t="n"/>
-      <c r="C6" s="10" t="str">
+      <c r="C6" s="11">
         <f>IF(OR($A6="",$B6=""),"",$B6-$A6+1)</f>
-      </c>
-      <c r="D6" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D6" s="12">
         <f>IF($A6="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A6,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E6" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E6" s="13">
         <f>IF($A6="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A6,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F6" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F6" s="11">
         <f>IF($A6="","",IF(DAY(DATE(YEAR($A6),2,29))=29,366,365))</f>
-      </c>
-      <c r="G6" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G6" s="12">
         <f>IF(OR($A6="",$E6="",$C6=""),"",ROUND($D6*$E6/100*$C6/$F6,2))</f>
-      </c>
-      <c r="H6" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H6" s="14">
         <f>IF($A6="","",IF(YEAR($A6)&lt;&gt;YEAR($B6),"Период пересекает 31 декабря — разбейте на две строки",IF($B6&lt;$A6,"Конец периода раньше начала",IF(OR($B5="",$A6&lt;&gt;$B5+1),"Период пропущен или перекрыт — исправьте даты",IF($E6="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
       <c r="B7" s="6" t="n"/>
-      <c r="C7" s="10" t="str">
+      <c r="C7" s="11">
         <f>IF(OR($A7="",$B7=""),"",$B7-$A7+1)</f>
-      </c>
-      <c r="D7" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D7" s="12">
         <f>IF($A7="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A7,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E7" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E7" s="13">
         <f>IF($A7="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A7,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F7" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F7" s="11">
         <f>IF($A7="","",IF(DAY(DATE(YEAR($A7),2,29))=29,366,365))</f>
-      </c>
-      <c r="G7" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G7" s="12">
         <f>IF(OR($A7="",$E7="",$C7=""),"",ROUND($D7*$E7/100*$C7/$F7,2))</f>
-      </c>
-      <c r="H7" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H7" s="14">
         <f>IF($A7="","",IF(YEAR($A7)&lt;&gt;YEAR($B7),"Период пересекает 31 декабря — разбейте на две строки",IF($B7&lt;$A7,"Конец периода раньше начала",IF(OR($B6="",$A7&lt;&gt;$B6+1),"Период пропущен или перекрыт — исправьте даты",IF($E7="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="10" t="str">
+      <c r="C8" s="11">
         <f>IF(OR($A8="",$B8=""),"",$B8-$A8+1)</f>
-      </c>
-      <c r="D8" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D8" s="12">
         <f>IF($A8="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A8,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E8" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E8" s="13">
         <f>IF($A8="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A8,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F8" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F8" s="11">
         <f>IF($A8="","",IF(DAY(DATE(YEAR($A8),2,29))=29,366,365))</f>
-      </c>
-      <c r="G8" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G8" s="12">
         <f>IF(OR($A8="",$E8="",$C8=""),"",ROUND($D8*$E8/100*$C8/$F8,2))</f>
-      </c>
-      <c r="H8" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H8" s="14">
         <f>IF($A8="","",IF(YEAR($A8)&lt;&gt;YEAR($B8),"Период пересекает 31 декабря — разбейте на две строки",IF($B8&lt;$A8,"Конец периода раньше начала",IF(OR($B7="",$A8&lt;&gt;$B7+1),"Период пропущен или перекрыт — исправьте даты",IF($E8="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
       <c r="B9" s="6" t="n"/>
-      <c r="C9" s="10" t="str">
+      <c r="C9" s="11">
         <f>IF(OR($A9="",$B9=""),"",$B9-$A9+1)</f>
-      </c>
-      <c r="D9" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D9" s="12">
         <f>IF($A9="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A9,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E9" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E9" s="13">
         <f>IF($A9="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A9,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F9" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F9" s="11">
         <f>IF($A9="","",IF(DAY(DATE(YEAR($A9),2,29))=29,366,365))</f>
-      </c>
-      <c r="G9" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G9" s="12">
         <f>IF(OR($A9="",$E9="",$C9=""),"",ROUND($D9*$E9/100*$C9/$F9,2))</f>
-      </c>
-      <c r="H9" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H9" s="14">
         <f>IF($A9="","",IF(YEAR($A9)&lt;&gt;YEAR($B9),"Период пересекает 31 декабря — разбейте на две строки",IF($B9&lt;$A9,"Конец периода раньше начала",IF(OR($B8="",$A9&lt;&gt;$B8+1),"Период пропущен или перекрыт — исправьте даты",IF($E9="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="10" t="str">
+      <c r="C10" s="11">
         <f>IF(OR($A10="",$B10=""),"",$B10-$A10+1)</f>
-      </c>
-      <c r="D10" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D10" s="12">
         <f>IF($A10="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A10,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E10" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E10" s="13">
         <f>IF($A10="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A10,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F10" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F10" s="11">
         <f>IF($A10="","",IF(DAY(DATE(YEAR($A10),2,29))=29,366,365))</f>
-      </c>
-      <c r="G10" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G10" s="12">
         <f>IF(OR($A10="",$E10="",$C10=""),"",ROUND($D10*$E10/100*$C10/$F10,2))</f>
-      </c>
-      <c r="H10" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H10" s="14">
         <f>IF($A10="","",IF(YEAR($A10)&lt;&gt;YEAR($B10),"Период пересекает 31 декабря — разбейте на две строки",IF($B10&lt;$A10,"Конец периода раньше начала",IF(OR($B9="",$A10&lt;&gt;$B9+1),"Период пропущен или перекрыт — исправьте даты",IF($E10="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
       <c r="B11" s="6" t="n"/>
-      <c r="C11" s="10" t="str">
+      <c r="C11" s="11">
         <f>IF(OR($A11="",$B11=""),"",$B11-$A11+1)</f>
-      </c>
-      <c r="D11" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D11" s="12">
         <f>IF($A11="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A11,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E11" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E11" s="13">
         <f>IF($A11="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A11,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F11" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F11" s="11">
         <f>IF($A11="","",IF(DAY(DATE(YEAR($A11),2,29))=29,366,365))</f>
-      </c>
-      <c r="G11" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G11" s="12">
         <f>IF(OR($A11="",$E11="",$C11=""),"",ROUND($D11*$E11/100*$C11/$F11,2))</f>
-      </c>
-      <c r="H11" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H11" s="14">
         <f>IF($A11="","",IF(YEAR($A11)&lt;&gt;YEAR($B11),"Период пересекает 31 декабря — разбейте на две строки",IF($B11&lt;$A11,"Конец периода раньше начала",IF(OR($B10="",$A11&lt;&gt;$B10+1),"Период пропущен или перекрыт — исправьте даты",IF($E11="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
       <c r="B12" s="6" t="n"/>
-      <c r="C12" s="10" t="str">
+      <c r="C12" s="11">
         <f>IF(OR($A12="",$B12=""),"",$B12-$A12+1)</f>
-      </c>
-      <c r="D12" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D12" s="12">
         <f>IF($A12="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A12,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E12" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E12" s="13">
         <f>IF($A12="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A12,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F12" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F12" s="11">
         <f>IF($A12="","",IF(DAY(DATE(YEAR($A12),2,29))=29,366,365))</f>
-      </c>
-      <c r="G12" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G12" s="12">
         <f>IF(OR($A12="",$E12="",$C12=""),"",ROUND($D12*$E12/100*$C12/$F12,2))</f>
-      </c>
-      <c r="H12" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H12" s="14">
         <f>IF($A12="","",IF(YEAR($A12)&lt;&gt;YEAR($B12),"Период пересекает 31 декабря — разбейте на две строки",IF($B12&lt;$A12,"Конец периода раньше начала",IF(OR($B11="",$A12&lt;&gt;$B11+1),"Период пропущен или перекрыт — исправьте даты",IF($E12="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
       <c r="B13" s="6" t="n"/>
-      <c r="C13" s="10" t="str">
+      <c r="C13" s="11">
         <f>IF(OR($A13="",$B13=""),"",$B13-$A13+1)</f>
-      </c>
-      <c r="D13" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D13" s="12">
         <f>IF($A13="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A13,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E13" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E13" s="13">
         <f>IF($A13="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A13,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F13" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F13" s="11">
         <f>IF($A13="","",IF(DAY(DATE(YEAR($A13),2,29))=29,366,365))</f>
-      </c>
-      <c r="G13" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G13" s="12">
         <f>IF(OR($A13="",$E13="",$C13=""),"",ROUND($D13*$E13/100*$C13/$F13,2))</f>
-      </c>
-      <c r="H13" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H13" s="14">
         <f>IF($A13="","",IF(YEAR($A13)&lt;&gt;YEAR($B13),"Период пересекает 31 декабря — разбейте на две строки",IF($B13&lt;$A13,"Конец периода раньше начала",IF(OR($B12="",$A13&lt;&gt;$B12+1),"Период пропущен или перекрыт — исправьте даты",IF($E13="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
       <c r="B14" s="6" t="n"/>
-      <c r="C14" s="10" t="str">
+      <c r="C14" s="11">
         <f>IF(OR($A14="",$B14=""),"",$B14-$A14+1)</f>
-      </c>
-      <c r="D14" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D14" s="12">
         <f>IF($A14="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A14,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E14" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E14" s="13">
         <f>IF($A14="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A14,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F14" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F14" s="11">
         <f>IF($A14="","",IF(DAY(DATE(YEAR($A14),2,29))=29,366,365))</f>
-      </c>
-      <c r="G14" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G14" s="12">
         <f>IF(OR($A14="",$E14="",$C14=""),"",ROUND($D14*$E14/100*$C14/$F14,2))</f>
-      </c>
-      <c r="H14" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H14" s="14">
         <f>IF($A14="","",IF(YEAR($A14)&lt;&gt;YEAR($B14),"Период пересекает 31 декабря — разбейте на две строки",IF($B14&lt;$A14,"Конец периода раньше начала",IF(OR($B13="",$A14&lt;&gt;$B13+1),"Период пропущен или перекрыт — исправьте даты",IF($E14="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
       <c r="B15" s="6" t="n"/>
-      <c r="C15" s="10" t="str">
+      <c r="C15" s="11">
         <f>IF(OR($A15="",$B15=""),"",$B15-$A15+1)</f>
-      </c>
-      <c r="D15" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D15" s="12">
         <f>IF($A15="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A15,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E15" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E15" s="13">
         <f>IF($A15="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A15,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F15" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F15" s="11">
         <f>IF($A15="","",IF(DAY(DATE(YEAR($A15),2,29))=29,366,365))</f>
-      </c>
-      <c r="G15" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G15" s="12">
         <f>IF(OR($A15="",$E15="",$C15=""),"",ROUND($D15*$E15/100*$C15/$F15,2))</f>
-      </c>
-      <c r="H15" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H15" s="14">
         <f>IF($A15="","",IF(YEAR($A15)&lt;&gt;YEAR($B15),"Период пересекает 31 декабря — разбейте на две строки",IF($B15&lt;$A15,"Конец периода раньше начала",IF(OR($B14="",$A15&lt;&gt;$B14+1),"Период пропущен или перекрыт — исправьте даты",IF($E15="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="6" t="n"/>
-      <c r="C16" s="10" t="str">
+      <c r="C16" s="11">
         <f>IF(OR($A16="",$B16=""),"",$B16-$A16+1)</f>
-      </c>
-      <c r="D16" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D16" s="12">
         <f>IF($A16="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A16,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E16" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E16" s="13">
         <f>IF($A16="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A16,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F16" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F16" s="11">
         <f>IF($A16="","",IF(DAY(DATE(YEAR($A16),2,29))=29,366,365))</f>
-      </c>
-      <c r="G16" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G16" s="12">
         <f>IF(OR($A16="",$E16="",$C16=""),"",ROUND($D16*$E16/100*$C16/$F16,2))</f>
-      </c>
-      <c r="H16" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H16" s="14">
         <f>IF($A16="","",IF(YEAR($A16)&lt;&gt;YEAR($B16),"Период пересекает 31 декабря — разбейте на две строки",IF($B16&lt;$A16,"Конец периода раньше начала",IF(OR($B15="",$A16&lt;&gt;$B15+1),"Период пропущен или перекрыт — исправьте даты",IF($E16="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
       <c r="B17" s="6" t="n"/>
-      <c r="C17" s="10" t="str">
+      <c r="C17" s="11">
         <f>IF(OR($A17="",$B17=""),"",$B17-$A17+1)</f>
-      </c>
-      <c r="D17" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D17" s="12">
         <f>IF($A17="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A17,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E17" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E17" s="13">
         <f>IF($A17="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A17,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F17" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F17" s="11">
         <f>IF($A17="","",IF(DAY(DATE(YEAR($A17),2,29))=29,366,365))</f>
-      </c>
-      <c r="G17" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G17" s="12">
         <f>IF(OR($A17="",$E17="",$C17=""),"",ROUND($D17*$E17/100*$C17/$F17,2))</f>
-      </c>
-      <c r="H17" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H17" s="14">
         <f>IF($A17="","",IF(YEAR($A17)&lt;&gt;YEAR($B17),"Период пересекает 31 декабря — разбейте на две строки",IF($B17&lt;$A17,"Конец периода раньше начала",IF(OR($B16="",$A17&lt;&gt;$B16+1),"Период пропущен или перекрыт — исправьте даты",IF($E17="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
       <c r="B18" s="6" t="n"/>
-      <c r="C18" s="10" t="str">
+      <c r="C18" s="11">
         <f>IF(OR($A18="",$B18=""),"",$B18-$A18+1)</f>
-      </c>
-      <c r="D18" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D18" s="12">
         <f>IF($A18="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A18,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E18" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E18" s="13">
         <f>IF($A18="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A18,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F18" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F18" s="11">
         <f>IF($A18="","",IF(DAY(DATE(YEAR($A18),2,29))=29,366,365))</f>
-      </c>
-      <c r="G18" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G18" s="12">
         <f>IF(OR($A18="",$E18="",$C18=""),"",ROUND($D18*$E18/100*$C18/$F18,2))</f>
-      </c>
-      <c r="H18" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H18" s="14">
         <f>IF($A18="","",IF(YEAR($A18)&lt;&gt;YEAR($B18),"Период пересекает 31 декабря — разбейте на две строки",IF($B18&lt;$A18,"Конец периода раньше начала",IF(OR($B17="",$A18&lt;&gt;$B17+1),"Период пропущен или перекрыт — исправьте даты",IF($E18="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
       <c r="B19" s="6" t="n"/>
-      <c r="C19" s="10" t="str">
+      <c r="C19" s="11">
         <f>IF(OR($A19="",$B19=""),"",$B19-$A19+1)</f>
-      </c>
-      <c r="D19" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D19" s="12">
         <f>IF($A19="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A19,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E19" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E19" s="13">
         <f>IF($A19="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A19,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F19" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F19" s="11">
         <f>IF($A19="","",IF(DAY(DATE(YEAR($A19),2,29))=29,366,365))</f>
-      </c>
-      <c r="G19" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G19" s="12">
         <f>IF(OR($A19="",$E19="",$C19=""),"",ROUND($D19*$E19/100*$C19/$F19,2))</f>
-      </c>
-      <c r="H19" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H19" s="14">
         <f>IF($A19="","",IF(YEAR($A19)&lt;&gt;YEAR($B19),"Период пересекает 31 декабря — разбейте на две строки",IF($B19&lt;$A19,"Конец периода раньше начала",IF(OR($B18="",$A19&lt;&gt;$B18+1),"Период пропущен или перекрыт — исправьте даты",IF($E19="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
       <c r="B20" s="6" t="n"/>
-      <c r="C20" s="10" t="str">
+      <c r="C20" s="11">
         <f>IF(OR($A20="",$B20=""),"",$B20-$A20+1)</f>
-      </c>
-      <c r="D20" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D20" s="12">
         <f>IF($A20="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A20,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E20" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E20" s="13">
         <f>IF($A20="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A20,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F20" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F20" s="11">
         <f>IF($A20="","",IF(DAY(DATE(YEAR($A20),2,29))=29,366,365))</f>
-      </c>
-      <c r="G20" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G20" s="12">
         <f>IF(OR($A20="",$E20="",$C20=""),"",ROUND($D20*$E20/100*$C20/$F20,2))</f>
-      </c>
-      <c r="H20" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H20" s="14">
         <f>IF($A20="","",IF(YEAR($A20)&lt;&gt;YEAR($B20),"Период пересекает 31 декабря — разбейте на две строки",IF($B20&lt;$A20,"Конец периода раньше начала",IF(OR($B19="",$A20&lt;&gt;$B19+1),"Период пропущен или перекрыт — исправьте даты",IF($E20="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
       <c r="B21" s="6" t="n"/>
-      <c r="C21" s="10" t="str">
+      <c r="C21" s="11">
         <f>IF(OR($A21="",$B21=""),"",$B21-$A21+1)</f>
-      </c>
-      <c r="D21" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D21" s="12">
         <f>IF($A21="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A21,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E21" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E21" s="13">
         <f>IF($A21="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A21,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F21" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F21" s="11">
         <f>IF($A21="","",IF(DAY(DATE(YEAR($A21),2,29))=29,366,365))</f>
-      </c>
-      <c r="G21" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G21" s="12">
         <f>IF(OR($A21="",$E21="",$C21=""),"",ROUND($D21*$E21/100*$C21/$F21,2))</f>
-      </c>
-      <c r="H21" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H21" s="14">
         <f>IF($A21="","",IF(YEAR($A21)&lt;&gt;YEAR($B21),"Период пересекает 31 декабря — разбейте на две строки",IF($B21&lt;$A21,"Конец периода раньше начала",IF(OR($B20="",$A21&lt;&gt;$B20+1),"Период пропущен или перекрыт — исправьте даты",IF($E21="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
       <c r="B22" s="6" t="n"/>
-      <c r="C22" s="10" t="str">
+      <c r="C22" s="11">
         <f>IF(OR($A22="",$B22=""),"",$B22-$A22+1)</f>
-      </c>
-      <c r="D22" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D22" s="12">
         <f>IF($A22="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A22,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E22" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E22" s="13">
         <f>IF($A22="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A22,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F22" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F22" s="11">
         <f>IF($A22="","",IF(DAY(DATE(YEAR($A22),2,29))=29,366,365))</f>
-      </c>
-      <c r="G22" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G22" s="12">
         <f>IF(OR($A22="",$E22="",$C22=""),"",ROUND($D22*$E22/100*$C22/$F22,2))</f>
-      </c>
-      <c r="H22" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H22" s="14">
         <f>IF($A22="","",IF(YEAR($A22)&lt;&gt;YEAR($B22),"Период пересекает 31 декабря — разбейте на две строки",IF($B22&lt;$A22,"Конец периода раньше начала",IF(OR($B21="",$A22&lt;&gt;$B21+1),"Период пропущен или перекрыт — исправьте даты",IF($E22="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
       <c r="B23" s="6" t="n"/>
-      <c r="C23" s="10" t="str">
+      <c r="C23" s="11">
         <f>IF(OR($A23="",$B23=""),"",$B23-$A23+1)</f>
-      </c>
-      <c r="D23" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D23" s="12">
         <f>IF($A23="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A23,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E23" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E23" s="13">
         <f>IF($A23="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A23,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F23" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F23" s="11">
         <f>IF($A23="","",IF(DAY(DATE(YEAR($A23),2,29))=29,366,365))</f>
-      </c>
-      <c r="G23" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G23" s="12">
         <f>IF(OR($A23="",$E23="",$C23=""),"",ROUND($D23*$E23/100*$C23/$F23,2))</f>
-      </c>
-      <c r="H23" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H23" s="14">
         <f>IF($A23="","",IF(YEAR($A23)&lt;&gt;YEAR($B23),"Период пересекает 31 декабря — разбейте на две строки",IF($B23&lt;$A23,"Конец периода раньше начала",IF(OR($B22="",$A23&lt;&gt;$B22+1),"Период пропущен или перекрыт — исправьте даты",IF($E23="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
       <c r="B24" s="6" t="n"/>
-      <c r="C24" s="10" t="str">
+      <c r="C24" s="11">
         <f>IF(OR($A24="",$B24=""),"",$B24-$A24+1)</f>
-      </c>
-      <c r="D24" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D24" s="12">
         <f>IF($A24="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A24,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E24" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E24" s="13">
         <f>IF($A24="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A24,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F24" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F24" s="11">
         <f>IF($A24="","",IF(DAY(DATE(YEAR($A24),2,29))=29,366,365))</f>
-      </c>
-      <c r="G24" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G24" s="12">
         <f>IF(OR($A24="",$E24="",$C24=""),"",ROUND($D24*$E24/100*$C24/$F24,2))</f>
-      </c>
-      <c r="H24" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H24" s="14">
         <f>IF($A24="","",IF(YEAR($A24)&lt;&gt;YEAR($B24),"Период пересекает 31 декабря — разбейте на две строки",IF($B24&lt;$A24,"Конец периода раньше начала",IF(OR($B23="",$A24&lt;&gt;$B23+1),"Период пропущен или перекрыт — исправьте даты",IF($E24="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
       <c r="B25" s="6" t="n"/>
-      <c r="C25" s="10" t="str">
+      <c r="C25" s="11">
         <f>IF(OR($A25="",$B25=""),"",$B25-$A25+1)</f>
-      </c>
-      <c r="D25" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D25" s="12">
         <f>IF($A25="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A25,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E25" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E25" s="13">
         <f>IF($A25="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A25,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F25" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F25" s="11">
         <f>IF($A25="","",IF(DAY(DATE(YEAR($A25),2,29))=29,366,365))</f>
-      </c>
-      <c r="G25" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G25" s="12">
         <f>IF(OR($A25="",$E25="",$C25=""),"",ROUND($D25*$E25/100*$C25/$F25,2))</f>
-      </c>
-      <c r="H25" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H25" s="14">
         <f>IF($A25="","",IF(YEAR($A25)&lt;&gt;YEAR($B25),"Период пересекает 31 декабря — разбейте на две строки",IF($B25&lt;$A25,"Конец периода раньше начала",IF(OR($B24="",$A25&lt;&gt;$B24+1),"Период пропущен или перекрыт — исправьте даты",IF($E25="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
       <c r="B26" s="6" t="n"/>
-      <c r="C26" s="10" t="str">
+      <c r="C26" s="11">
         <f>IF(OR($A26="",$B26=""),"",$B26-$A26+1)</f>
-      </c>
-      <c r="D26" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D26" s="12">
         <f>IF($A26="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A26,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E26" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E26" s="13">
         <f>IF($A26="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A26,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F26" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F26" s="11">
         <f>IF($A26="","",IF(DAY(DATE(YEAR($A26),2,29))=29,366,365))</f>
-      </c>
-      <c r="G26" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G26" s="12">
         <f>IF(OR($A26="",$E26="",$C26=""),"",ROUND($D26*$E26/100*$C26/$F26,2))</f>
-      </c>
-      <c r="H26" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H26" s="14">
         <f>IF($A26="","",IF(YEAR($A26)&lt;&gt;YEAR($B26),"Период пересекает 31 декабря — разбейте на две строки",IF($B26&lt;$A26,"Конец периода раньше начала",IF(OR($B25="",$A26&lt;&gt;$B25+1),"Период пропущен или перекрыт — исправьте даты",IF($E26="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
       <c r="B27" s="6" t="n"/>
-      <c r="C27" s="10" t="str">
+      <c r="C27" s="11">
         <f>IF(OR($A27="",$B27=""),"",$B27-$A27+1)</f>
-      </c>
-      <c r="D27" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D27" s="12">
         <f>IF($A27="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A27,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E27" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E27" s="13">
         <f>IF($A27="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A27,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F27" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F27" s="11">
         <f>IF($A27="","",IF(DAY(DATE(YEAR($A27),2,29))=29,366,365))</f>
-      </c>
-      <c r="G27" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G27" s="12">
         <f>IF(OR($A27="",$E27="",$C27=""),"",ROUND($D27*$E27/100*$C27/$F27,2))</f>
-      </c>
-      <c r="H27" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H27" s="14">
         <f>IF($A27="","",IF(YEAR($A27)&lt;&gt;YEAR($B27),"Период пересекает 31 декабря — разбейте на две строки",IF($B27&lt;$A27,"Конец периода раньше начала",IF(OR($B26="",$A27&lt;&gt;$B26+1),"Период пропущен или перекрыт — исправьте даты",IF($E27="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
       <c r="B28" s="6" t="n"/>
-      <c r="C28" s="10" t="str">
+      <c r="C28" s="11">
         <f>IF(OR($A28="",$B28=""),"",$B28-$A28+1)</f>
-      </c>
-      <c r="D28" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D28" s="12">
         <f>IF($A28="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A28,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E28" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E28" s="13">
         <f>IF($A28="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A28,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F28" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F28" s="11">
         <f>IF($A28="","",IF(DAY(DATE(YEAR($A28),2,29))=29,366,365))</f>
-      </c>
-      <c r="G28" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G28" s="12">
         <f>IF(OR($A28="",$E28="",$C28=""),"",ROUND($D28*$E28/100*$C28/$F28,2))</f>
-      </c>
-      <c r="H28" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H28" s="14">
         <f>IF($A28="","",IF(YEAR($A28)&lt;&gt;YEAR($B28),"Период пересекает 31 декабря — разбейте на две строки",IF($B28&lt;$A28,"Конец периода раньше начала",IF(OR($B27="",$A28&lt;&gt;$B27+1),"Период пропущен или перекрыт — исправьте даты",IF($E28="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
       <c r="B29" s="6" t="n"/>
-      <c r="C29" s="10" t="str">
+      <c r="C29" s="11">
         <f>IF(OR($A29="",$B29=""),"",$B29-$A29+1)</f>
-      </c>
-      <c r="D29" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D29" s="12">
         <f>IF($A29="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A29,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E29" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E29" s="13">
         <f>IF($A29="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A29,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F29" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F29" s="11">
         <f>IF($A29="","",IF(DAY(DATE(YEAR($A29),2,29))=29,366,365))</f>
-      </c>
-      <c r="G29" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G29" s="12">
         <f>IF(OR($A29="",$E29="",$C29=""),"",ROUND($D29*$E29/100*$C29/$F29,2))</f>
-      </c>
-      <c r="H29" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H29" s="14">
         <f>IF($A29="","",IF(YEAR($A29)&lt;&gt;YEAR($B29),"Период пересекает 31 декабря — разбейте на две строки",IF($B29&lt;$A29,"Конец периода раньше начала",IF(OR($B28="",$A29&lt;&gt;$B28+1),"Период пропущен или перекрыт — исправьте даты",IF($E29="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
       <c r="B30" s="6" t="n"/>
-      <c r="C30" s="10" t="str">
+      <c r="C30" s="11">
         <f>IF(OR($A30="",$B30=""),"",$B30-$A30+1)</f>
-      </c>
-      <c r="D30" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D30" s="12">
         <f>IF($A30="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A30,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E30" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E30" s="13">
         <f>IF($A30="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A30,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F30" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F30" s="11">
         <f>IF($A30="","",IF(DAY(DATE(YEAR($A30),2,29))=29,366,365))</f>
-      </c>
-      <c r="G30" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G30" s="12">
         <f>IF(OR($A30="",$E30="",$C30=""),"",ROUND($D30*$E30/100*$C30/$F30,2))</f>
-      </c>
-      <c r="H30" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H30" s="14">
         <f>IF($A30="","",IF(YEAR($A30)&lt;&gt;YEAR($B30),"Период пересекает 31 декабря — разбейте на две строки",IF($B30&lt;$A30,"Конец периода раньше начала",IF(OR($B29="",$A30&lt;&gt;$B29+1),"Период пропущен или перекрыт — исправьте даты",IF($E30="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
       <c r="B31" s="6" t="n"/>
-      <c r="C31" s="10" t="str">
+      <c r="C31" s="11">
         <f>IF(OR($A31="",$B31=""),"",$B31-$A31+1)</f>
-      </c>
-      <c r="D31" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D31" s="12">
         <f>IF($A31="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A31,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E31" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E31" s="13">
         <f>IF($A31="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A31,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F31" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F31" s="11">
         <f>IF($A31="","",IF(DAY(DATE(YEAR($A31),2,29))=29,366,365))</f>
-      </c>
-      <c r="G31" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G31" s="12">
         <f>IF(OR($A31="",$E31="",$C31=""),"",ROUND($D31*$E31/100*$C31/$F31,2))</f>
-      </c>
-      <c r="H31" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H31" s="14">
         <f>IF($A31="","",IF(YEAR($A31)&lt;&gt;YEAR($B31),"Период пересекает 31 декабря — разбейте на две строки",IF($B31&lt;$A31,"Конец периода раньше начала",IF(OR($B30="",$A31&lt;&gt;$B30+1),"Период пропущен или перекрыт — исправьте даты",IF($E31="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
       <c r="B32" s="6" t="n"/>
-      <c r="C32" s="10" t="str">
+      <c r="C32" s="11">
         <f>IF(OR($A32="",$B32=""),"",$B32-$A32+1)</f>
-      </c>
-      <c r="D32" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D32" s="12">
         <f>IF($A32="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A32,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E32" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E32" s="13">
         <f>IF($A32="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A32,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F32" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F32" s="11">
         <f>IF($A32="","",IF(DAY(DATE(YEAR($A32),2,29))=29,366,365))</f>
-      </c>
-      <c r="G32" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G32" s="12">
         <f>IF(OR($A32="",$E32="",$C32=""),"",ROUND($D32*$E32/100*$C32/$F32,2))</f>
-      </c>
-      <c r="H32" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H32" s="14">
         <f>IF($A32="","",IF(YEAR($A32)&lt;&gt;YEAR($B32),"Период пересекает 31 декабря — разбейте на две строки",IF($B32&lt;$A32,"Конец периода раньше начала",IF(OR($B31="",$A32&lt;&gt;$B31+1),"Период пропущен или перекрыт — исправьте даты",IF($E32="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
       <c r="B33" s="6" t="n"/>
-      <c r="C33" s="10" t="str">
+      <c r="C33" s="11">
         <f>IF(OR($A33="",$B33=""),"",$B33-$A33+1)</f>
-      </c>
-      <c r="D33" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D33" s="12">
         <f>IF($A33="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A33,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E33" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E33" s="13">
         <f>IF($A33="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A33,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F33" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F33" s="11">
         <f>IF($A33="","",IF(DAY(DATE(YEAR($A33),2,29))=29,366,365))</f>
-      </c>
-      <c r="G33" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G33" s="12">
         <f>IF(OR($A33="",$E33="",$C33=""),"",ROUND($D33*$E33/100*$C33/$F33,2))</f>
-      </c>
-      <c r="H33" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H33" s="14">
         <f>IF($A33="","",IF(YEAR($A33)&lt;&gt;YEAR($B33),"Период пересекает 31 декабря — разбейте на две строки",IF($B33&lt;$A33,"Конец периода раньше начала",IF(OR($B32="",$A33&lt;&gt;$B32+1),"Период пропущен или перекрыт — исправьте даты",IF($E33="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
       <c r="B34" s="6" t="n"/>
-      <c r="C34" s="10" t="str">
+      <c r="C34" s="11">
         <f>IF(OR($A34="",$B34=""),"",$B34-$A34+1)</f>
-      </c>
-      <c r="D34" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D34" s="12">
         <f>IF($A34="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A34,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E34" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E34" s="13">
         <f>IF($A34="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A34,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F34" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F34" s="11">
         <f>IF($A34="","",IF(DAY(DATE(YEAR($A34),2,29))=29,366,365))</f>
-      </c>
-      <c r="G34" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G34" s="12">
         <f>IF(OR($A34="",$E34="",$C34=""),"",ROUND($D34*$E34/100*$C34/$F34,2))</f>
-      </c>
-      <c r="H34" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H34" s="14">
         <f>IF($A34="","",IF(YEAR($A34)&lt;&gt;YEAR($B34),"Период пересекает 31 декабря — разбейте на две строки",IF($B34&lt;$A34,"Конец периода раньше начала",IF(OR($B33="",$A34&lt;&gt;$B33+1),"Период пропущен или перекрыт — исправьте даты",IF($E34="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
       <c r="B35" s="6" t="n"/>
-      <c r="C35" s="10" t="str">
+      <c r="C35" s="11">
         <f>IF(OR($A35="",$B35=""),"",$B35-$A35+1)</f>
-      </c>
-      <c r="D35" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D35" s="12">
         <f>IF($A35="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A35,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E35" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E35" s="13">
         <f>IF($A35="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A35,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F35" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F35" s="11">
         <f>IF($A35="","",IF(DAY(DATE(YEAR($A35),2,29))=29,366,365))</f>
-      </c>
-      <c r="G35" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G35" s="12">
         <f>IF(OR($A35="",$E35="",$C35=""),"",ROUND($D35*$E35/100*$C35/$F35,2))</f>
-      </c>
-      <c r="H35" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H35" s="14">
         <f>IF($A35="","",IF(YEAR($A35)&lt;&gt;YEAR($B35),"Период пересекает 31 декабря — разбейте на две строки",IF($B35&lt;$A35,"Конец периода раньше начала",IF(OR($B34="",$A35&lt;&gt;$B34+1),"Период пропущен или перекрыт — исправьте даты",IF($E35="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
       <c r="B36" s="6" t="n"/>
-      <c r="C36" s="10" t="str">
+      <c r="C36" s="11">
         <f>IF(OR($A36="",$B36=""),"",$B36-$A36+1)</f>
-      </c>
-      <c r="D36" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D36" s="12">
         <f>IF($A36="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A36,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E36" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E36" s="13">
         <f>IF($A36="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A36,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F36" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F36" s="11">
         <f>IF($A36="","",IF(DAY(DATE(YEAR($A36),2,29))=29,366,365))</f>
-      </c>
-      <c r="G36" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G36" s="12">
         <f>IF(OR($A36="",$E36="",$C36=""),"",ROUND($D36*$E36/100*$C36/$F36,2))</f>
-      </c>
-      <c r="H36" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H36" s="14">
         <f>IF($A36="","",IF(YEAR($A36)&lt;&gt;YEAR($B36),"Период пересекает 31 декабря — разбейте на две строки",IF($B36&lt;$A36,"Конец периода раньше начала",IF(OR($B35="",$A36&lt;&gt;$B35+1),"Период пропущен или перекрыт — исправьте даты",IF($E36="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
       <c r="B37" s="6" t="n"/>
-      <c r="C37" s="10" t="str">
+      <c r="C37" s="11">
         <f>IF(OR($A37="",$B37=""),"",$B37-$A37+1)</f>
-      </c>
-      <c r="D37" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D37" s="12">
         <f>IF($A37="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A37,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E37" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E37" s="13">
         <f>IF($A37="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A37,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F37" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F37" s="11">
         <f>IF($A37="","",IF(DAY(DATE(YEAR($A37),2,29))=29,366,365))</f>
-      </c>
-      <c r="G37" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G37" s="12">
         <f>IF(OR($A37="",$E37="",$C37=""),"",ROUND($D37*$E37/100*$C37/$F37,2))</f>
-      </c>
-      <c r="H37" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H37" s="14">
         <f>IF($A37="","",IF(YEAR($A37)&lt;&gt;YEAR($B37),"Период пересекает 31 декабря — разбейте на две строки",IF($B37&lt;$A37,"Конец периода раньше начала",IF(OR($B36="",$A37&lt;&gt;$B36+1),"Период пропущен или перекрыт — исправьте даты",IF($E37="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
       <c r="B38" s="6" t="n"/>
-      <c r="C38" s="10" t="str">
+      <c r="C38" s="11">
         <f>IF(OR($A38="",$B38=""),"",$B38-$A38+1)</f>
-      </c>
-      <c r="D38" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D38" s="12">
         <f>IF($A38="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A38,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E38" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E38" s="13">
         <f>IF($A38="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A38,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F38" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F38" s="11">
         <f>IF($A38="","",IF(DAY(DATE(YEAR($A38),2,29))=29,366,365))</f>
-      </c>
-      <c r="G38" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G38" s="12">
         <f>IF(OR($A38="",$E38="",$C38=""),"",ROUND($D38*$E38/100*$C38/$F38,2))</f>
-      </c>
-      <c r="H38" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H38" s="14">
         <f>IF($A38="","",IF(YEAR($A38)&lt;&gt;YEAR($B38),"Период пересекает 31 декабря — разбейте на две строки",IF($B38&lt;$A38,"Конец периода раньше начала",IF(OR($B37="",$A38&lt;&gt;$B37+1),"Период пропущен или перекрыт — исправьте даты",IF($E38="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
       <c r="B39" s="6" t="n"/>
-      <c r="C39" s="10" t="str">
+      <c r="C39" s="11">
         <f>IF(OR($A39="",$B39=""),"",$B39-$A39+1)</f>
-      </c>
-      <c r="D39" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D39" s="12">
         <f>IF($A39="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A39,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E39" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E39" s="13">
         <f>IF($A39="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A39,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F39" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F39" s="11">
         <f>IF($A39="","",IF(DAY(DATE(YEAR($A39),2,29))=29,366,365))</f>
-      </c>
-      <c r="G39" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G39" s="12">
         <f>IF(OR($A39="",$E39="",$C39=""),"",ROUND($D39*$E39/100*$C39/$F39,2))</f>
-      </c>
-      <c r="H39" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H39" s="14">
         <f>IF($A39="","",IF(YEAR($A39)&lt;&gt;YEAR($B39),"Период пересекает 31 декабря — разбейте на две строки",IF($B39&lt;$A39,"Конец периода раньше начала",IF(OR($B38="",$A39&lt;&gt;$B38+1),"Период пропущен или перекрыт — исправьте даты",IF($E39="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
       <c r="B40" s="6" t="n"/>
-      <c r="C40" s="10" t="str">
+      <c r="C40" s="11">
         <f>IF(OR($A40="",$B40=""),"",$B40-$A40+1)</f>
-      </c>
-      <c r="D40" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D40" s="12">
         <f>IF($A40="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A40,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E40" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E40" s="13">
         <f>IF($A40="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A40,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F40" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F40" s="11">
         <f>IF($A40="","",IF(DAY(DATE(YEAR($A40),2,29))=29,366,365))</f>
-      </c>
-      <c r="G40" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G40" s="12">
         <f>IF(OR($A40="",$E40="",$C40=""),"",ROUND($D40*$E40/100*$C40/$F40,2))</f>
-      </c>
-      <c r="H40" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H40" s="14">
         <f>IF($A40="","",IF(YEAR($A40)&lt;&gt;YEAR($B40),"Период пересекает 31 декабря — разбейте на две строки",IF($B40&lt;$A40,"Конец периода раньше начала",IF(OR($B39="",$A40&lt;&gt;$B39+1),"Период пропущен или перекрыт — исправьте даты",IF($E40="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
       <c r="B41" s="6" t="n"/>
-      <c r="C41" s="10" t="str">
+      <c r="C41" s="11">
         <f>IF(OR($A41="",$B41=""),"",$B41-$A41+1)</f>
-      </c>
-      <c r="D41" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D41" s="12">
         <f>IF($A41="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A41,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E41" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E41" s="13">
         <f>IF($A41="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A41,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F41" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F41" s="11">
         <f>IF($A41="","",IF(DAY(DATE(YEAR($A41),2,29))=29,366,365))</f>
-      </c>
-      <c r="G41" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G41" s="12">
         <f>IF(OR($A41="",$E41="",$C41=""),"",ROUND($D41*$E41/100*$C41/$F41,2))</f>
-      </c>
-      <c r="H41" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H41" s="14">
         <f>IF($A41="","",IF(YEAR($A41)&lt;&gt;YEAR($B41),"Период пересекает 31 декабря — разбейте на две строки",IF($B41&lt;$A41,"Конец периода раньше начала",IF(OR($B40="",$A41&lt;&gt;$B40+1),"Период пропущен или перекрыт — исправьте даты",IF($E41="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
       <c r="B42" s="6" t="n"/>
-      <c r="C42" s="10" t="str">
+      <c r="C42" s="11">
         <f>IF(OR($A42="",$B42=""),"",$B42-$A42+1)</f>
-      </c>
-      <c r="D42" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D42" s="12">
         <f>IF($A42="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A42,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E42" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E42" s="13">
         <f>IF($A42="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A42,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F42" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F42" s="11">
         <f>IF($A42="","",IF(DAY(DATE(YEAR($A42),2,29))=29,366,365))</f>
-      </c>
-      <c r="G42" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G42" s="12">
         <f>IF(OR($A42="",$E42="",$C42=""),"",ROUND($D42*$E42/100*$C42/$F42,2))</f>
-      </c>
-      <c r="H42" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H42" s="14">
         <f>IF($A42="","",IF(YEAR($A42)&lt;&gt;YEAR($B42),"Период пересекает 31 декабря — разбейте на две строки",IF($B42&lt;$A42,"Конец периода раньше начала",IF(OR($B41="",$A42&lt;&gt;$B41+1),"Период пропущен или перекрыт — исправьте даты",IF($E42="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
       <c r="B43" s="6" t="n"/>
-      <c r="C43" s="10" t="str">
+      <c r="C43" s="11">
         <f>IF(OR($A43="",$B43=""),"",$B43-$A43+1)</f>
-      </c>
-      <c r="D43" s="11" t="str">
+        <v/>
+      </c>
+      <c r="D43" s="12">
         <f>IF($A43="","",'Входные данные'!$B$4-SUMIF('Входные данные'!$A$35:$A$44,"&lt;"&amp;$A43,'Входные данные'!$B$35:$B$44))</f>
-      </c>
-      <c r="E43" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E43" s="13">
         <f>IF($A43="","",IFERROR(INDEX('Входные данные'!$B$12:$B$31,MATCH($A43,'Входные данные'!$A$12:$A$31,1)),""))</f>
-      </c>
-      <c r="F43" s="10" t="str">
+        <v/>
+      </c>
+      <c r="F43" s="11">
         <f>IF($A43="","",IF(DAY(DATE(YEAR($A43),2,29))=29,366,365))</f>
-      </c>
-      <c r="G43" s="11" t="str">
+        <v/>
+      </c>
+      <c r="G43" s="12">
         <f>IF(OR($A43="",$E43="",$C43=""),"",ROUND($D43*$E43/100*$C43/$F43,2))</f>
-      </c>
-      <c r="H43" s="13" t="str">
+        <v/>
+      </c>
+      <c r="H43" s="14">
         <f>IF($A43="","",IF(YEAR($A43)&lt;&gt;YEAR($B43),"Период пересекает 31 декабря — разбейте на две строки",IF($B43&lt;$A43,"Конец периода раньше начала",IF(OR($B42="",$A43&lt;&gt;$B42+1),"Период пропущен или перекрыт — исправьте даты",IF($E43="","Ставка на эту дату не найдена: дополните таблицу ставок","")))))</f>
+        <v/>
       </c>
     </row>
     <row r="45">
-      <c r="F45" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Проценты по ст. 395 ГК РФ, всего:</t>
-        </is>
-      </c>
-      <c r="G45" s="15" t="n">
+      <c r="F45" s="15" t="inlineStr">
+        <is>
+          <t>Проценты по ст. 395 ГК РФ, всего:</t>
+        </is>
+      </c>
+      <c r="G45" s="16">
         <f>ROUND(SUM($G$4:$G$43),2)</f>
-        <v>0</v>
-      </c>
-      <c r="H45" s="16" t="str">
+        <v/>
+      </c>
+      <c r="H45" s="17">
         <f>IF(COUNT($A$4:$A$43)=0,"",IF(MAX($B$4:$B$43)&lt;&gt;'Входные данные'!$B$6,"Последний период не совпадает с датой окончания",""))</f>
+        <v/>
       </c>
     </row>
     <row r="46">
-      <c r="F46" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Долг плюс проценты:</t>
-        </is>
-      </c>
-      <c r="G46" s="15" t="n">
+      <c r="F46" s="15" t="inlineStr">
+        <is>
+          <t>Долг плюс проценты:</t>
+        </is>
+      </c>
+      <c r="G46" s="16">
         <f>ROUND('Входные данные'!$B$4-SUM('Входные данные'!$B$35:$B$44)+$G$45,2)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="48" ht="46" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Число дней в году берётся фактическое — 365 или 366. Формула считает по фактическому числу дней; норму, которая устанавливала бы иной знаменатель, этот расчёт не применяет. Если для вашего спора знаменатель принципиален, сверьте его с юристом по действующей практике на дату расчёта.</t>
+          <t>Число дней в году берётся фактическое — 365 или 366. Формула считает по фактическому числу дней; норму, которая устанавливала бы иной знаменатель, этот расчёт не применяет. Если для вашего спора знаменатель принципиален, сверьте его с юристом по действующей практике на дату расчёта.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Проверьте себя перед отправкой</t>
+          <t>Проверьте себя перед отправкой</t>
         </is>
       </c>
     </row>
     <row r="51" ht="46" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сверьте итог с любым публичным калькулятором процентов по ст. 395 ГК РФ — например, в справочно-правовой системе. Расхождение больше копеек на округлении означает ошибку в разбивке периодов, а не в калькуляторе. Колонка «Проверка» должна быть пустой во всех заполненных строках.</t>
+          <t>Сверьте итог с любым публичным калькулятором процентов по ст. 395 ГК РФ — например, в справочно-правовой системе. Расхождение больше копеек на округлении означает ошибку в разбивке периодов, а не в калькуляторе. Колонка «Проверка» должна быть пустой во всех заполненных строках.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="2">
     <mergeCell ref="A48:H48"/>
     <mergeCell ref="A51:H51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Готовый блок для претензии или иска</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Значения подставляются сами. Лист печатается как приложение «Расчёт взыскиваемой суммы» — судьи ждут расчёт в разбивке по периодам, поэтому печатайте вместе с листом «Расчёт».</t>
+          <t>Готовый блок для претензии или иска</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="46" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Значения подставляются сами. Лист печатается как приложение «Расчёт взыскиваемой суммы» — судьи ждут расчёт в разбивке по периодам, поэтому печатайте вместе с листом «Расчёт».</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Сумма долга на начало расчёта, руб.</t>
-        </is>
-      </c>
-      <c r="B4" s="18" t="n">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>Сумма долга на начало расчёта, руб.</t>
+        </is>
+      </c>
+      <c r="B4" s="12">
         <f>'Входные данные'!$B$4</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Учтено частичных оплат, руб.</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="n">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>Учтено частичных оплат, руб.</t>
+        </is>
+      </c>
+      <c r="B5" s="12">
         <f>ROUND(SUM('Входные данные'!$B$35:$B$44),2)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Основной долг к взысканию, руб.</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="n">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>Основной долг к взысканию, руб.</t>
+        </is>
+      </c>
+      <c r="B6" s="12">
         <f>ROUND('Входные данные'!$B$4-SUM('Входные данные'!$B$35:$B$44),2)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Период начисления с</t>
-        </is>
-      </c>
-      <c r="B7" s="28" t="n">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>Период начисления с</t>
+        </is>
+      </c>
+      <c r="B7" s="19">
         <f>'Входные данные'!$B$5</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Период начисления по</t>
-        </is>
-      </c>
-      <c r="B8" s="28" t="n">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>Период начисления по</t>
+        </is>
+      </c>
+      <c r="B8" s="19">
         <f>'Входные данные'!$B$6</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Всего дней просрочки</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="str">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>Всего дней просрочки</t>
+        </is>
+      </c>
+      <c r="B9" s="20">
         <f>IF(OR('Входные данные'!$B$5="",'Входные данные'!$B$6=""),"",'Входные данные'!$B$6-'Входные данные'!$B$5+1)</f>
+        <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Проценты по ст. 395 ГК РФ, руб.</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="n">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>Проценты по ст. 395 ГК РФ, руб.</t>
+        </is>
+      </c>
+      <c r="B10" s="12">
         <f>'Расчёт'!$G$45</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Итого к взысканию, руб.</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="n">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>Итого к взысканию, руб.</t>
+        </is>
+      </c>
+      <c r="B11" s="12">
         <f>'Расчёт'!$G$46</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Фраза для документа</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
+          <t>Фраза для документа</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
       <c r="A13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Проценты подлежат начислению по день фактической уплаты долга (п. 3 ст. 395 ГК РФ).</t>
+          <t>Проценты подлежат начислению по день фактической уплаты долга (п. 3 ст. 395 ГК РФ).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что это не заменяет</t>
+          <t>Что это не заменяет</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">— Выбор между процентами по ст. 395 и договорной неустойкой. Если договором установлена неустойка за просрочку оплаты, по общему правилу взыскивается она (п. 4 ст. 395 ГК РФ) — выбор согласуйте с юристом.</t>
+          <t>— Выбор между процентами по ст. 395 и договорной неустойкой. Если договором установлена неустойка за просрочку оплаты, по общему правилу взыскивается она (п. 4 ст. 395 ГК РФ) — выбор согласуйте с юристом.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">— Учёт мораторных периодов, банкротства должника и иных оснований приостановки начисления. При таких обстоятельствах расчёт корректирует юрист.</t>
+          <t>— Учёт мораторных периодов, банкротства должника и иных оснований приостановки начисления. При таких обстоятельствах расчёт корректирует юрист.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="46" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">— Заключение специалиста. Суд проверяет расчёт сам; эта таблица — рабочий инструмент истца, а не доказательство само по себе.</t>
+          <t>— Заключение специалиста. Суд проверяет расчёт сам; эта таблица — рабочий инструмент истца, а не доказательство само по себе.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="46" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">— Юридическую консультацию и вычитку юристом. Порядок расчёта сверен с текстом действующих норм 16.08.2026: нормативная сверка сопоставляет формулировки и порядок со статьями закона и правовой позиции по вашему спору не оценивает.</t>
+          <t>— Юридическую консультацию и вычитку юристом. Порядок расчёта сверен с текстом действующих норм 16.08.2026: нормативная сверка сопоставляет формулировки и порядок со статьями закона и правовой позиции по вашему спору не оценивает.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="6">
     <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A18:B18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Пример: как выглядят заполненные поля</t>
+          <t>Пример: как выглядят заполненные поля</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Здесь показан формат ввода, а не ваш расчёт. Цифры вымышленные, ставки — условные: реальные берите на cbr.ru. Ничего отсюда не переносите в документ.</t>
+          <t>Здесь показан формат ввода, а не ваш расчёт. Цифры вымышленные, ставки — условные: реальные берите на cbr.ru. Ничего отсюда не переносите в документ.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Входные данные</t>
+          <t>Входные данные</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Сумма долга, руб.</t>
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>Сумма долга, руб.</t>
         </is>
       </c>
       <c r="B5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 250 000,00</t>
+          <t>1 250 000,00</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Дата начала просрочки</t>
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>Дата начала просрочки</t>
         </is>
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.03.2026</t>
+          <t>15.03.2026</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Дата окончания расчёта</t>
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>Дата окончания расчёта</t>
         </is>
       </c>
       <c r="B7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">30.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Таблица ставок</t>
+          <t>Таблица ставок</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Действует с</t>
+          <t>Действует с</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ставка, % годовых</t>
+          <t>Ставка, % годовых</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.03.2026</t>
+          <t>15.03.2026</t>
         </is>
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">условная 1</t>
+          <t>условная 1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">28.04.2026</t>
+          <t>28.04.2026</t>
         </is>
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">условная 2</t>
+          <t>условная 2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Строки листа «Расчёт»</t>
+          <t>Строки листа «Расчёт»</t>
         </is>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Начало периода</t>
-        </is>
-      </c>
-      <c r="B15" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Конец периода</t>
-        </is>
-      </c>
-      <c r="C15" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Дней в периоде</t>
-        </is>
-      </c>
-      <c r="D15" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">База долга, руб.</t>
-        </is>
-      </c>
-      <c r="E15" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ставка, % годовых</t>
-        </is>
-      </c>
-      <c r="F15" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Дней в году</t>
-        </is>
-      </c>
-      <c r="G15" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Проценты за период, руб.</t>
-        </is>
-      </c>
-      <c r="H15" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Проверка</t>
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>Начало периода</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>Конец периода</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>Дней в периоде</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>База долга, руб.</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>Ставка, % годовых</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>Дней в году</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>Проценты за период, руб.</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>Проверка</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15.03.2026</t>
-        </is>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27.04.2026</t>
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>15.03.2026</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
         </is>
       </c>
       <c r="C16" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">считается</t>
+          <t>считается</t>
         </is>
       </c>
       <c r="D16" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">считается</t>
+          <t>считается</t>
         </is>
       </c>
       <c r="E16" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">подставится</t>
+          <t>подставится</t>
         </is>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">считается</t>
+          <t>считается</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">считается</t>
+          <t>считается</t>
         </is>
       </c>
       <c r="H16" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">пусто, если всё верно</t>
+          <t>пусто, если всё верно</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28.04.2026</t>
-        </is>
-      </c>
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30.07.2026</t>
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="C17" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">считается</t>
+          <t>считается</t>
         </is>
       </c>
       <c r="D17" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">считается</t>
+          <t>считается</t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">подставится</t>
+          <t>подставится</t>
         </is>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">считается</t>
+          <t>считается</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">считается</t>
+          <t>считается</t>
         </is>
       </c>
       <c r="H17" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">пусто, если всё верно</t>
+          <t>пусто, если всё верно</t>
         </is>
       </c>
     </row>
     <row r="19" ht="46" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обратите внимание: период разбит на две строки по дате смены ставки. Если бы просрочка пересекала 31 декабря, разбить пришлось бы и там — колонка «Проверка» об этом напомнит.</t>
+          <t>Обратите внимание: период разбит на две строки по дате смены ставки. Если бы просрочка пересекала 31 декабря, разбить пришлось бы и там — колонка «Проверка» об этом напомнит.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="2">
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/products-storage/04-polnyy-komplekt-pto/01-30-bazovye-pakety/01-zakrytie-rabot/14-raschet-procentov-395-gk.xlsx
+++ b/products-storage/04-polnyy-komplekt-pto/01-30-bazovye-pakety/01-zakrytie-rabot/14-raschet-procentov-395-gk.xlsx
@@ -2026,7 +2026,7 @@
     <row r="51" ht="46" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Сверьте итог с любым публичным калькулятором процентов по ст. 395 ГК РФ — например, в справочно-правовой системе. Расхождение больше копеек на округлении означает ошибку в разбивке периодов, а не в калькуляторе. Колонка «Проверка» должна быть пустой во всех заполненных строках.</t>
+          <t>Сверьте итог с независимым расчётом процентов по ст. 395 ГК РФ, например в справочно-правовой системе. При расхождении проверьте ставки, даты, базу долга, разбивку периодов и округление в обоих расчётах. Колонка «Проверка» должна быть пустой во всех заполненных строках.</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
     <row r="19" ht="46" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>— Юридическую консультацию и вычитку юристом. Порядок расчёта сверен с текстом действующих норм 16.08.2026: нормативная сверка сопоставляет формулировки и порядок со статьями закона и правовой позиции по вашему спору не оценивает.</t>
+          <t>— Юридическую консультацию и вычитку юристом. Нормативная сверка сопоставляет формулировки и порядок со статьями закона и не заменяет проверку обстоятельств вашего спора.</t>
         </is>
       </c>
     </row>
